--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G673"/>
+  <dimension ref="A1:G676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14566,6 +14566,69 @@
         </is>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Oral Cancer Histopathological Image</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr"/>
+      <c r="C674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/samihamuntahamahin/oral-cancer-histopathological-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>shuvomonowar01/brats-2d-mri-segmentation</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr"/>
+      <c r="C675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/shuvomonowar01/brats-2d-mri-segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>IDEALTA-LIME: scan-level partitions, fused deep and handcrafted features, trained models and LIME explanations for pulmonary nodule classification on LUNA16</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr"/>
+      <c r="C676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22216090</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G676"/>
+  <dimension ref="A1:G679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14629,6 +14629,69 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>LSS MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr"/>
+      <c r="C677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/abid074/lss-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Dataset for Progesterone Receptor Ligand Binding Domain bound to Norethindrone</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr"/>
+      <c r="C678" t="inlineStr"/>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22211824</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Dataset for: Flux Growth and Anisotropic Magnetic Properties of FeMo2S4 Crystals</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr"/>
+      <c r="C679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22635322</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G679"/>
+  <dimension ref="A1:G683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14692,6 +14692,90 @@
         </is>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>brain mri tumor detection dataset training&amp;testing</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr"/>
+      <c r="C680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr"/>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/shukurohajani/brain-mri-tumor-detection-dataset-training-and-testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>SHERO Alzheimer's MRI PET Dataset</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr"/>
+      <c r="C681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sheemawani/shero-alzheimers-mri-pet</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Dataset from the Paper: "The Shape of Biological Metadata: Measuring Repository Richness with Entity-Based NLP Metrics"</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22229074</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Dual‐branch MRI denoising and motion artifact suppression with uncertainty estimation and segmentation‐based evaluation.</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr"/>
+      <c r="C683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr"/>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13548186/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G683"/>
+  <dimension ref="A1:G689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14776,6 +14776,132 @@
         </is>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>COCO Dental 31-Class Dataset</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr"/>
+      <c r="C684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/eriksmite/coco-dental-31class</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>FRPV-PH. Microscopy Image Dataset</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr"/>
+      <c r="C685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/user164919/microscopy-image-dataset-of-pulmonary-vessels</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Automated Brain Segmentation in Accelerated T2-Weighted MRI: Effects of Deep Learning-Based Reconstruction</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr"/>
+      <c r="C686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22664823</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Multiscale Remote Sensing and Ground Truth Dataset for Mine Waste Characterisation at Memi Mine, Republic of Cyprus (m4mining project)</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr"/>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22251025</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Dataset for "X-ray driven displacive excitation of coherent phonons"</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr"/>
+      <c r="C688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22647167</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Dataset Routine Fluoroscopy-Guided Arthrocentesis Under Sedation prior to Revision Total Hip Arthroplasty</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr"/>
+      <c r="C689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Fluoroscopy</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22657967</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G689"/>
+  <dimension ref="A1:G695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14902,6 +14902,132 @@
         </is>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Mendeley Dataset</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr"/>
+      <c r="C690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="inlineStr"/>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/saifuddinreadoy123/mendeley-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>19-Class Stool Parasite Dataset</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr"/>
+      <c r="C691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/haripriyajayasankar/19-class-stool-microscopy-parasite-detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>PAD-UFES-20 Clinical Skin Lesion Dataset</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr"/>
+      <c r="C692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/soumydastopper/pad-ufes-20-clinical-skin-lesion-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>GACELLE: GPU-accelerated tools for model parameter estimation and image reconstruction example dataset</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr"/>
+      <c r="C693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22666992</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>SEM micrographs for human-in-the-loop segmentation and classification</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr"/>
+      <c r="C694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22243033</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Dataset and Code for: Metabolic Gating and the Evolution of Human Cognitive Plasticity: A Comparative Genomic Analysis</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr"/>
+      <c r="C695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22676625</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G695"/>
+  <dimension ref="A1:G705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15028,6 +15028,216 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Brain Tumor Classification MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr"/>
+      <c r="C696" t="inlineStr"/>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr"/>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/saifuddinreadoy123/brain-tumor-classification-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Brain tumor MRI image for Fedarated Learning</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr"/>
+      <c r="C697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/saifuddinreadoy123/brain-tumor-mri-image-for-fedarated-learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Connectome 2.0 550 µm multi-shot spiral and EPI dMRI data and images</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr"/>
+      <c r="C698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>dMRI</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22699967</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>FARD: Multi-Contrast MRI Acceleration Dataset (T1/T2/FLAIR, LR/HR/Bicubic)</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr"/>
+      <c r="C699" t="inlineStr"/>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr"/>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22692564</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>TotalSegmentator MRI dataset: 1296 MRI images with segmentations for 50 anatomical regions</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr"/>
+      <c r="C700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr"/>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22688334</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Simulated X-ray particle tracking velocimetry dataset for direct trajectory reconstruction validation</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr"/>
+      <c r="C701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr"/>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22675822</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Comparing tangible retinal image characteristics with deep learning features reveals their complementarity for gene association and disease prediction — figure data</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr"/>
+      <c r="C702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Retinal Image</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr"/>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22706413</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Dataset for publication Structure-Guided Modulation of the Optical and Mechanical Properties of Ultrathin Poly(γ-benzyl-L-glutamate)-Based Membranes</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr"/>
+      <c r="C703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr"/>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22704383</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>napari Workshop Teaching Dataset: Spatially Downsampled Images, Detections, and Tracks.</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr"/>
+      <c r="C704" t="inlineStr"/>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22696913</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Conditioning-noise regularization for diffusion-based artifact detection in histopathology — model outputs and evaluation data</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr"/>
+      <c r="C705" t="inlineStr"/>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22702800</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G705"/>
+  <dimension ref="A1:G709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15238,6 +15238,90 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>ZnO-GO Composite Dataset for ML</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr"/>
+      <c r="C706" t="inlineStr"/>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/muhammadwaseemashraf/zno-go-composite-dataset-for-ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>EDEN2020 In Vivo Ovine Brain MRI Dataset: Diffusion Tensor Imaging and T1-Weighted Images Before and After Intraparenchymal Infusion</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr"/>
+      <c r="C707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22696052</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Data and analysis for "Internal adaptation of CAD/CAM post-and-core restorations using prefabricated versus digitally derived scan posts: an in vitro micro-CT analysis"</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr"/>
+      <c r="C708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22708403</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Dataset from switching loss measurement test bench by opposition method</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr"/>
+      <c r="C709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22708072</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G709"/>
+  <dimension ref="A1:G712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15322,6 +15322,69 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>M4 MRI Motion-Corrupted Dataset Step 68</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr"/>
+      <c r="C710" t="inlineStr"/>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr"/>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nitin0903/m4-mri-motion-step68</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Parkinson Dataset Brain MRI Image</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr"/>
+      <c r="C711" t="inlineStr"/>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mdmaskathossain/parkinson-dataset-brain-mri-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Luxar benchmark volumes: sixteen of the seventeen microscopy volumes analysed in the Luxar manuscript (as consumed by the analyses)</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr"/>
+      <c r="C712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22682970</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G712"/>
+  <dimension ref="A1:G717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15385,6 +15385,111 @@
         </is>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>MRI DATASET</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr"/>
+      <c r="C713" t="inlineStr"/>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rituuukumar/mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>DERM12345 Skin Lesion Dataset</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr"/>
+      <c r="C714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mohammadmiraj/derm12345-skin-lesion-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>niclasclassen/segmentations-of-distended-and-collapsed-colons-from-ct-scans</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr"/>
+      <c r="C715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr"/>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/niclasclassen/segmentations-of-distended-and-collapsed-colons-from-ct-scans</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Explainable Hybrid Swin-Unet for Trustworthy Multi-Class Brain Tumor Classification: Curated MRI Dataset, Code, and Supporting Materials</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr"/>
+      <c r="C716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr"/>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22736644</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Timing-Aware Acquisition for Sequential Readout of Distributed Hall-Sensor Nodes in Low-Field MRI Firmware/Software/Dataset</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr"/>
+      <c r="C717" t="inlineStr"/>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/20752863</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G717"/>
+  <dimension ref="A1:G727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15490,6 +15490,216 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Millionaire Habits Dataset</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr"/>
+      <c r="C718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/datascikhan/millionaire-habits-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Chest X-Ray Images</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr"/>
+      <c r="C719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/chauvvan/chest-x-ray-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Dental X-Ray Image</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr"/>
+      <c r="C720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mohammadrezaseyfpour/dental-x-ray-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>ayeshaamin/NEU-Feces-Microscopy-Dataset</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr"/>
+      <c r="C721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/ayeshaamin/NEU-Feces-Microscopy-Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Dataset for "Efficient and selective copper extraction from legacy carbonate-rich tailings using alkaline glycine leaching"</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr"/>
+      <c r="C722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22751161</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Coherence-Gated 3D Refractive Index Reconstruction Using Volumetric Quantitative Transmission Optical Coherence Tomography - Dataset</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr"/>
+      <c r="C723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22727474</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>De-identified dataset supporting: Bowel Preparation for Same-Day Bidirectional Endoscopy Improves Gastric Mucosal Visualization: A Retrospective Cohort Study</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr"/>
+      <c r="C724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr"/>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22754737</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Temporal Deconvolution of Mesoscale Recordings: Synthetic Dataset, Inference Method Implementations, and Analysis Scripts</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr"/>
+      <c r="C725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr"/>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22755873</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Dataset for article Functionalization and performance of stainless steel 316L using ultrasonically excited Pulsating Water Jet peening</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr"/>
+      <c r="C726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr"/>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/19918860</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (62-study corpus)</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr"/>
+      <c r="C727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr"/>
+      <c r="F727" t="inlineStr"/>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22750077</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G727"/>
+  <dimension ref="A1:G732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15700,6 +15700,111 @@
         </is>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Unified Skin Lesion Segmentation Dataset</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr"/>
+      <c r="C728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr"/>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ghuy1201/unified-skin-lesion-segmentation-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Visible Korean male head dataset: sectioned images, segmented images, 7.0 T MRI data, and 3D models</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr"/>
+      <c r="C729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr"/>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22759852</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Iceberg rafted debris counts from computed tomography scan imagery of International Ocean Discovery Program Site U1524 cores 1 and 2</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr"/>
+      <c r="C730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr"/>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22769128</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Linked collectors and determiners for: Records of the DAFWA Plant Pathology Collection.</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr"/>
+      <c r="C731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22783387</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>INTELKAMAT - Cervical Colposcopy Image Dataset</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr"/>
+      <c r="C732" t="inlineStr"/>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22768429</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G732"/>
+  <dimension ref="A1:G739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15805,6 +15805,153 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>HCD ConvNeXt Tiny Train dataset with wsi column</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr"/>
+      <c r="C733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/pavlozelinskiy/hcd-convnext-tiny-train-dataset-with-wsi-column</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Dataset for "Efficient and selective copper extraction from legacy carbonate-rich tailings using alkaline glycine leaching"</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr"/>
+      <c r="C734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22810625</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Dataset for: Charge Transfer to Solvent Modulated by pH-dependent Hydrogen Bonding</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr"/>
+      <c r="C735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr"/>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22773570</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Dataset from switching loss measurement test bench by opposition method</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr"/>
+      <c r="C736" t="inlineStr"/>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22799087</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Dataset for: State-Dependent 3D Enhancer Architecture Resolves a Shared Schizophrenia and Multiple Sclerosis Ketone and Lactate Sensing Logic Gate</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr"/>
+      <c r="C737" t="inlineStr"/>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr"/>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22795362</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Endovis26 SQ-AI CVSP-NTUA</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr"/>
+      <c r="C738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Laparoscopy</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn77426536</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Production Pipeline Implementation in Student Short Films (2024–2026)</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr"/>
+      <c r="C739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/1TELVU</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G739"/>
+  <dimension ref="A1:G744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15952,6 +15952,111 @@
         </is>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>TCGA-ESCA  Dataset</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr"/>
+      <c r="C740" t="inlineStr"/>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/saibhossain/tcga-esca-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Dataset for: Template-Directed Stepwise Growth of WS2 on Sr2SnO4: Interfacial Electronic Engineering for High-Performance Sensing and Energy Storage</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr"/>
+      <c r="C741" t="inlineStr"/>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr"/>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22813785</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Luxar benchmark volumes: sixteen of the seventeen microscopy volumes analysed in the Luxar manuscript (as consumed by the analyses)</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr"/>
+      <c r="C742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr"/>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22820799</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Raw microscopy images and source data for "Entry exclusion enables selective conjugative DNA delivery in synthetic bacterial communities"</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr"/>
+      <c r="C743" t="inlineStr"/>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22820958</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Multi-sensor 3D data fusion dataset for historical building pathology: TLS, multispectral, and thermal point clouds of Santa María de Melque visigothic church (Toledo, Spain)</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr"/>
+      <c r="C744" t="inlineStr"/>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22810830</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G744"/>
+  <dimension ref="A1:G748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16057,6 +16057,90 @@
         </is>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Lungs Cancer Classification -CT Scan images</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr"/>
+      <c r="C745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nvnkhan/lungs-cancer-classification-ct-scan-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>A Novel Laplace Transform-Based Symmetric Encryption Framework with Hyperbolic Sine Coefficient Embedding and Position-Dependent Keystream for Secure and Numerically Lossless Medical Image Protection</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr"/>
+      <c r="C746" t="inlineStr"/>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22843132</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Dataset and code for automated label-free quality control of hiPSC-derived neuronal cultures</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr"/>
+      <c r="C747" t="inlineStr"/>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22812687</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Dataset for: State-Dependent 3D Enhancer Architecture Resolves a Shared Schizophrenia and Multiple Sclerosis Ketone and Lactate Sensing Logic Gate</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr"/>
+      <c r="C748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22831446</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G748"/>
+  <dimension ref="A1:G750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16141,6 +16141,48 @@
         </is>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>UMUD Challenge dataset</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr"/>
+      <c r="C749" t="inlineStr"/>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nagatakengo/segmentation-baseline-models</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>okbro1234/NSCLC-THESIS-WSI-DATASET-EMBEDDING</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr"/>
+      <c r="C750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/okbro1234/NSCLC-THESIS-WSI-DATASET-EMBEDDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G750"/>
+  <dimension ref="A1:G756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16183,6 +16183,132 @@
         </is>
       </c>
     </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Multimodal Cardiac CT–MRI Diagnosis Dataset</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr"/>
+      <c r="C751" t="inlineStr"/>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr"/>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rajsharg/multimodal-cardiac-ctmri-diagnosis-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Breast Histopathology Images</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr"/>
+      <c r="C752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/lunarco/breast-histopathology-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Dataset for Eye Movements and the Intraorbital Subarachnoid Space  in Optic Neuropathy</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr"/>
+      <c r="C753" t="inlineStr"/>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/12729634</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Optimisation of measurement and data analysis of time-resolved X-ray absorption spectroscopy of thin film organic semiconductors - Dataset</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr"/>
+      <c r="C754" t="inlineStr"/>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22876087</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>USE OF AN ARTIFICIAL INTELLIGENCE ASSISTANT FOR DETECTING BONE FRACTURES ON RADIOGRAPHIC IMAGES: DIAGNOSTIC ACCURACY AND DECISION SUPPORT</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr"/>
+      <c r="C755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22880534</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Dataset for: In vitro pre-vascularized model of the human skin based on collagen hydrogel reinforced by fibrin-coated nanofibrous membrane</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr"/>
+      <c r="C756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21218676</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G756"/>
+  <dimension ref="A1:G765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16309,6 +16309,195 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>MRI Brain Tumor Dataset 40K Merged</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr"/>
+      <c r="C757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nushraa/denoised-ds-merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>US Mortgage Borrower Readiness Dataset</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr"/>
+      <c r="C758" t="inlineStr"/>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ournethelps/us-mortgage-borrower-readiness-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Learn2Breath Train Val Dataset</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr"/>
+      <c r="C759" t="inlineStr"/>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ahmedashrafhelmi/learn2breath-train-val-data</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Dental Dataset</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr"/>
+      <c r="C760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/suhrathtahra/dental-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>skin-lesion-segmentation-classification</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr"/>
+      <c r="C761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/unlimitedera/skin-lesion-segmentation-classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Ham 10,000 balanced Dataset</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr"/>
+      <c r="C762" t="inlineStr"/>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr"/>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sharadvyas/ham-10000-balanced-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Dataset for: In vitro pre-vascularized model of the human skin based on collagen hydrogel reinforced by fibrin-coated nanofibrous membrane</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr"/>
+      <c r="C763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr"/>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22902208</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>SEM images of diatom-rich laminated sediments from the deglacial of South Georgia</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr"/>
+      <c r="C764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22898009</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Bialystok Outline Annotated Cervical Cytology Dataset</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr"/>
+      <c r="C765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr"/>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21948494</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G765"/>
+  <dimension ref="A1:G779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16498,6 +16498,300 @@
         </is>
       </c>
     </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>treasurenleanya/tuberculosis-tb-chest-xray-dataset</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr"/>
+      <c r="C766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr"/>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/treasurenleanya/tuberculosis-tb-chest-xray-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>treasurenleanya/chest-xray-dataset</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr"/>
+      <c r="C767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr"/>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/treasurenleanya/chest-xray-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>treasurenleanya/nigeria-chest-x-ray-dataset</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr"/>
+      <c r="C768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr"/>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/treasurenleanya/nigeria-chest-x-ray-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>treasurenleanya/bus-uclm-breast-ultrasound-dataset</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr"/>
+      <c r="C769" t="inlineStr"/>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/treasurenleanya/bus-uclm-breast-ultrasound-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>treasurenleanya/breast-ultrasound-images-dataset</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr"/>
+      <c r="C770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr"/>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/treasurenleanya/breast-ultrasound-images-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>treasurenleanya/bus-bra-a-breast-ultrasound-dataset</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr"/>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr"/>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/treasurenleanya/bus-bra-a-breast-ultrasound-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Curated Dataset of 430 Studies on fMRI-to-Image Reconstruction A PRISMA 2020-Guided Systematic Review and Bibliometric Analysis</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr"/>
+      <c r="C772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr"/>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22086597</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Acetylcholinesterase (AChE) interaction whit the amyloid PET tracer Pittsburgh Compound B (PiB) dataset</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr"/>
+      <c r="C773" t="inlineStr"/>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr"/>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22937353</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Dataset of preprocessed NII- and DTI-derived metrics from patients with FMS and health controls with sedentary lifestyles</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr"/>
+      <c r="C774" t="inlineStr"/>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr"/>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22927724</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Multi-Anatomical Ultrafast Ultrasound Dataset: Raw RF Signals acquired with a GE 11L-D probe</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr"/>
+      <c r="C775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr"/>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22936172</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>USE OF AN ARTIFICIAL INTELLIGENCE ASSISTANT FOR DETECTING BONE FRACTURES ON RADIOGRAPHIC IMAGES: DIAGNOSTIC ACCURACY AND DECISION SUPPORT</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr"/>
+      <c r="C776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr"/>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22916263</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>EARLY DETECTION OF CARDIOVASCULAR DISEASES IN CHILDREN: CLINICAL SCREENING, MODERN INSTRUMENTAL DIAGNOSTICS, AND ASSESSMENT OF RISK FACTORS</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr"/>
+      <c r="C777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr"/>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22922330</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Dataset of the paper "Deep Generative Models for Enhanced Vitreous OCT Imaging"</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr"/>
+      <c r="C778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr"/>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22914426</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>NEONATAL PERIOD PATHOLOGIES IN NEWBORNS: RISK FACTORS, EARLY DETECTION, INTENSIVE MONITORING AND MODERN PREVENTIVE OPPORTUNITIES</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr"/>
+      <c r="C779" t="inlineStr"/>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr"/>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22930045</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G779"/>
+  <dimension ref="A1:G787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16792,6 +16792,174 @@
         </is>
       </c>
     </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Movie Dataset (MocTale Format)</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr"/>
+      <c r="C780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr"/>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/aakashdandekar/movie-dataset-moctale-format</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Dartmouth Lung Cancer Histology Dataset</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr"/>
+      <c r="C781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr"/>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/baivabmukherjee/dhmc-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>OpenSkeleton: Open, Sex-Specific Full-Body Skeletal dataset for Statistical Shape Modeling</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr"/>
+      <c r="C782" t="inlineStr"/>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr"/>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22833546</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>INTEGRATED CLINICAL, ULTRASONOGRAPHIC, AND IMMUNOHISTOCHEMICAL RISK STRATIFICATION OF ASYMPTOMATIC OVARIAN MASSES IN POSTMENOPAUSAL WOMEN: EARLY DETECTION OF MALIGNANCY AND PROGNOSTIC ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr"/>
+      <c r="C783" t="inlineStr"/>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Immunohistochemistry</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr"/>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22956376</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Synthetic AI-READI Dataset for T2DM Research</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr"/>
+      <c r="C784" t="inlineStr"/>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22944362</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Physical-chemical dataset during the West Wind Drift Cruise during spring 2018</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr"/>
+      <c r="C785" t="inlineStr"/>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr"/>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/17364216</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (62-study corpus)</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr"/>
+      <c r="C786" t="inlineStr"/>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22957730</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Derived Data, Phikon Embeddings, and Analysis Code for "Calibration-Aware Patient-Level Prediction of Source-Defined MSIMUT Status in Colorectal Cancer from Whole-Slide Histopathology Images Using Foundation-Model Embeddings"</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr"/>
+      <c r="C787" t="inlineStr"/>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22938170</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G787"/>
+  <dimension ref="A1:G790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16960,6 +16960,69 @@
         </is>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>ERAF4XRD: a 273-document benchmark for automated extraction of X-ray diffraction figures and metadata from the published literature</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr"/>
+      <c r="C788" t="inlineStr"/>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22683615</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Classification of CSC2.1.1 unknown X-ray sources from "Self-Organizing Maps for the Exploration and Classification of X-Ray Sources in the Chandra Source Catalog"</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr"/>
+      <c r="C789" t="inlineStr"/>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/20932855</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Skin-Lesion Classification</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr"/>
+      <c r="C790" t="inlineStr"/>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22961240</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G790"/>
+  <dimension ref="A1:G793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17023,6 +17023,69 @@
         </is>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>MILK10k: Clinical &amp;Dermoscopic Skin Lesion Dataset</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr"/>
+      <c r="C791" t="inlineStr"/>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/muhammadhamzamaher/milk10k-clinical-and-dermoscopic-skin-lesion-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>MULTIMODAL CLINICAL-IMAGING DATASET FOR RISK STRATIFICATION OF SOLITARY PULMONARY LESIONS USING ARTIFICIAL INTELLIGENCE</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr"/>
+      <c r="C792" t="inlineStr"/>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22983972</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Example dataset for SiLM</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr"/>
+      <c r="C793" t="inlineStr"/>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22985803</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G793"/>
+  <dimension ref="A1:G797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17086,6 +17086,90 @@
         </is>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Combined Brain MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr"/>
+      <c r="C794" t="inlineStr"/>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ishikabhardwaj009/combined-brain-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Multimodal Emotion Dataset: Video, EEG, ECG &amp; EMG</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr"/>
+      <c r="C795" t="inlineStr"/>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ajithdari/multimodal-emotion-dataset-video-eeg-ecg-and-emg</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Per-image results and trained models for: Recovering Silently Missed Small Lesions in Colonoscopy and Thyroid Ultrasound Segmentation Under Domain Shift</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr"/>
+      <c r="C796" t="inlineStr"/>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23002629</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Dataset of CFD simulations, particle trajectories, mesh-independence analyses, experimental validation, and image-processing workflows for inertial droplet separation in spiral microchannels</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr"/>
+      <c r="C797" t="inlineStr"/>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22997492</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G797"/>
+  <dimension ref="A1:G801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17170,6 +17170,90 @@
         </is>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Vindr-pcxr-dataset custom</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr"/>
+      <c r="C798" t="inlineStr"/>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/shamimulislamsunny/vindr-pcxr-dataset-custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Retinal OCT Cognitive Dataset</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr"/>
+      <c r="C799" t="inlineStr"/>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/commcollabs/retinal-oct-cognitive-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>HEAR-MRI: helix-tragus-junction and nasion fiducials on structural MRI across nine EEG–MRI cohorts, with a cross-cohort detection benchmark</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr"/>
+      <c r="C800" t="inlineStr"/>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>sMRI</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23020254</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>SEP-PRISM Data:   A multi-source dataset for solar energetic particle forecasting</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr"/>
+      <c r="C801" t="inlineStr"/>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22844972</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G801"/>
+  <dimension ref="A1:G806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17254,6 +17254,111 @@
         </is>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Fundus Images for Retinopathy of Prematurity(ROP)</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr"/>
+      <c r="C802" t="inlineStr"/>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ucimachinelearning/retinopathy-of-prematurity-rop-fundus-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Data and analysis for "Internal adaptation of CAD/CAM post-and-core restorations using prefabricated versus digitally derived scan posts: an in vitro micro-CT analysis"</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr"/>
+      <c r="C803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23055164</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>A 22,266-Image Grazing-Incidence Wide-Angle X-ray Scattering Benchmark Dataset for Organic Photovoltaic and Perovskite Materials Characterization</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr"/>
+      <c r="C804" t="inlineStr"/>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22657132</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (79-study corpus, manuscript v0.3.3)</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr"/>
+      <c r="C805" t="inlineStr"/>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23059484</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Stain Interventions as Pipeline-Dependent Components: Workflow, Metric, and Reference Sensitivity in Cross-Dataset Nuclei Instance Segmentation</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr"/>
+      <c r="C806" t="inlineStr"/>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22996314</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G806"/>
+  <dimension ref="A1:G832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17359,6 +17359,552 @@
         </is>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>MRI scans for brain tumor</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr"/>
+      <c r="C807" t="inlineStr"/>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/hrigvedprabhu/mri-scans-for-brain-tumor</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>cmr consolidated dataset</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr"/>
+      <c r="C808" t="inlineStr"/>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/aninamullan/consolidated-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Vindr -PCXR- Custom Dataset for ssl</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr"/>
+      <c r="C809" t="inlineStr"/>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/shamimulislamsunny/vindr-pcxr-custom-dataset-for-ssl</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Prohibited Item Detection: A Large-Scale X-ray</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr"/>
+      <c r="C810" t="inlineStr"/>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/magatijr/prohibited-item-detection-a-large-scale-x-ray</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Indian Stocks Comprehensive Fundamentals Dataset</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr"/>
+      <c r="C811" t="inlineStr"/>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ayushkhaire/indian-stocks-comprehensive-fundamentals-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Skin lesion Dataset</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr"/>
+      <c r="C812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/bhavesh1207/skin-lesion-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>kindredbluespirit/xvla-oct26-draft-dataset</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr"/>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/kindredbluespirit/xvla-oct26-draft-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Dataset for "Physics- and Data-driven reduced-order modeling of spatiotemporal pleural pressure distribution"</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr"/>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21821594</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Bayesian Image Reconstruction with Spatially Variant PSFs in X-ray Astronomy</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr"/>
+      <c r="C815" t="inlineStr"/>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22741106</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Integrated Geophysical, Geochemical, Geotechnical and Machine-Learning Dataset for Clay-Mineral Characterisation in the Western Niger Delta, Nigeria</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr"/>
+      <c r="C816" t="inlineStr"/>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23048702</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Code and data accompanying the article "Measuring Data Leakage in the Absence of Patient Identifiers: A Public Kidney CT Benchmark and a Transferable Screen"</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr"/>
+      <c r="C817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23101877</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Common carotid artery intima media ultrasound images</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr"/>
+      <c r="C818" t="inlineStr"/>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23098462</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Dataset: The limits of ensemble perception: Hierarchical grouping and object-based encoding</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr"/>
+      <c r="C819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23066548</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>A standadised dataset of endoscopy images in gynaecological cancer</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr"/>
+      <c r="C820" t="inlineStr"/>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23023497</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>DOSE-I: A Multimodal Biosignal Dataset of Procedural Sedation for Endoscopy</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr"/>
+      <c r="C821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22145442</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Dataset for Article: "Surface State Decouples Normal Detachment and Slip Initiation in Grip-Optimized Rubber Contacts"</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr"/>
+      <c r="C822" t="inlineStr"/>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22671100</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>AxonPath datasets: annotated electron microscopy and brightfield images of myelinated nerve fibres</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr"/>
+      <c r="C823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23084690</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Dataset from the analyses on: Molecular Adaptations and Metabolic Reprogramming of Priestia megaterium KW16 in Response to Fungal Pathogen-Derived Filtrates</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr"/>
+      <c r="C824" t="inlineStr"/>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23061968</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Lacey carbon grid image dataset</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr"/>
+      <c r="C825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23062808</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (79-study corpus, manuscript v0.3.6)</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr"/>
+      <c r="C826" t="inlineStr"/>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23071998</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Code, data and models for: Tissue Detection Determines False Positives in Diffusion-Based Histopathology Artifact Detection</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr"/>
+      <c r="C827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23016733</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Comparative evaluation of VoxelMorpand conventional deformable image registration algorithms for thoracic 4D-CT in radiotherapy.</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr"/>
+      <c r="C828" t="inlineStr"/>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr"/>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13598922/</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>A Wavelet-Based Framework for Mapping Long Memory in Resting-State fMRI: Age-Related Changes in the Hippocampus From the ADHD-200 Dataset.</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr"/>
+      <c r="C829" t="inlineStr"/>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr"/>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13586012/</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>149. Segmentation guided deep learning for sperm morphology classification in bull breeding soundness examinations.</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr"/>
+      <c r="C830" t="inlineStr"/>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr"/>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13620624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Vaitkunas Materials (Basel Switzerland) 2026 (Pubmed ID 42195557)</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr"/>
+      <c r="C831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr"/>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn77750156</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Chronic wounds multimodal image database</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr"/>
+      <c r="C832" t="inlineStr"/>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr"/>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/6A1HAG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G832"/>
+  <dimension ref="A1:G837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17905,6 +17905,111 @@
         </is>
       </c>
     </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>pidray-x-ray-image-dataset-academic-uses</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr"/>
+      <c r="C833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr"/>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/magatimunyambo/pidray-x-ray-image-dataset-academic-uses</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Esophageal Cancer Endoscopy Image Dataset</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr"/>
+      <c r="C834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr"/>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ucimachinelearning/esophageal-cancer-endoscopy-image-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Confocal microscopy images of human adipose-derived mesenchymal stem cells exposed to palmitate: mitochondrial membrane potential (JC-1), mitochondrial superoxide (mtSOX Deep Red), mitochondrial network (MitoBright LT Green) and mitophagy (Mitophagy Dye)</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr"/>
+      <c r="C835" t="inlineStr"/>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Confocal Microscopy</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr"/>
+      <c r="F835" t="inlineStr"/>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23112402</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Microscopy images of microglia, astrocytes and oligodendrocyte-lineage cells used to validate Microcount, an open-source MATLAB application for glial cell segmentation and morphological analysis</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr"/>
+      <c r="C836" t="inlineStr"/>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr"/>
+      <c r="F836" t="inlineStr"/>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23090918</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>L929-PhC: Annotated Phase-Contrast Microscopy Dataset for Automated Cell Detection and Counting</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr"/>
+      <c r="C837" t="inlineStr"/>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr"/>
+      <c r="F837" t="inlineStr"/>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23103970</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G837"/>
+  <dimension ref="A1:G841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18010,6 +18010,90 @@
         </is>
       </c>
     </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Non-Contrast to Contrast MRI Translation Dataset</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr"/>
+      <c r="C838" t="inlineStr"/>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr"/>
+      <c r="F838" t="inlineStr"/>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/berkutayasan/non-contrast-to-contrast-mri-translation-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Mridul-Dixit/chessmind-arena-policy-dataset</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr"/>
+      <c r="C839" t="inlineStr"/>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr"/>
+      <c r="F839" t="inlineStr"/>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/Mridul-Dixit/chessmind-arena-policy-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Deep-Fish-Bone: Brightfield Microscopy Dataset for Multi-Label Segmentation of Craniovertebral Skeletal Structures in Zebrafish Larvae</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr"/>
+      <c r="C840" t="inlineStr"/>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr"/>
+      <c r="F840" t="inlineStr"/>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23125004</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Reference Image, Development Workflow, and Metric Choice Shape the Apparent Benefit of Stain Normalization in Cross-Dataset Nuclei Instance Segmentation: Reproducibility Archive</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr"/>
+      <c r="C841" t="inlineStr"/>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr"/>
+      <c r="F841" t="inlineStr"/>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23132741</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G841"/>
+  <dimension ref="A1:G843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18094,6 +18094,48 @@
         </is>
       </c>
     </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>FracAtlas: Musculoskeletal Fracture X-ray Dataset</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr"/>
+      <c r="C842" t="inlineStr"/>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr"/>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ornob22/fracatlas-musculoskeletal-fracture-x-ray-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Histology Tissue Fold Dataset with Pixel-Level Annotations for Artificial Intelligence-Based Detection and Segmentation of Tissue Fold Artifacts in H&amp;E-Stained Teaching Slides</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr"/>
+      <c r="C843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>H&amp;E</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr"/>
+      <c r="F843" t="inlineStr"/>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22107895</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G843"/>
+  <dimension ref="A1:G850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18136,6 +18136,153 @@
         </is>
       </c>
     </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>BCMID Breast Cancer Multimodal Imaging Dataset</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr"/>
+      <c r="C844" t="inlineStr"/>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/aymendhieb1/bcmid-breast-cancer-multimodal-imaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Simultaneous transabdominal EHG and dynamic MRI dataset for uterine–bladder source separation (anatomical surfaces, electrode positions, and MRI bladder signals)</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr"/>
+      <c r="C845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr"/>
+      <c r="F845" t="inlineStr"/>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23183772</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Diffusion MRI metrics (FA, MD, NDI, ODI) from a longitudinal study of CSF1R-haploinsufficient female mice: supplementary dataset for Schmidt et al. (Neurobiology of Disease)</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr"/>
+      <c r="C846" t="inlineStr"/>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>dMRI</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr"/>
+      <c r="F846" t="inlineStr"/>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23129686</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Diffusion MRI metrics (FA, MD, NDI, ODI) from a longitudinal study of CSF1R-haploinsufficient male mice: supplementary dataset for Schmidt et al. (Neurobiology of Disease)</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr"/>
+      <c r="C847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>dMRI</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr"/>
+      <c r="F847" t="inlineStr"/>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23158683</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Developmental brain fibre architecture:confocal images and quantitative data</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr"/>
+      <c r="C848" t="inlineStr"/>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Confocal Microscopy</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr"/>
+      <c r="F848" t="inlineStr"/>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23178725</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>BEETLE: A multicentric dataset for training and benchmarking breast cancer segmentation in H&amp;E slides</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr"/>
+      <c r="C849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>H&amp;E</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr"/>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22751764</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Skin-Lesion Classification</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr"/>
+      <c r="C850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr"/>
+      <c r="F850" t="inlineStr"/>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23168489</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G850"/>
+  <dimension ref="A1:G862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18283,6 +18283,258 @@
         </is>
       </c>
     </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Brain Tumor Classification (MRI)</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr"/>
+      <c r="C851" t="inlineStr"/>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr"/>
+      <c r="F851" t="inlineStr"/>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/abdelrazeksheta/brain-tumor-classification-mri</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>JTuong/U-net-Chest-X-ray-Dataset-withLung-Segmentation</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr"/>
+      <c r="C852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr"/>
+      <c r="F852" t="inlineStr"/>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/JTuong/U-net-Chest-X-ray-Dataset-withLung-Segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Open-Access Multimodal Dataset of Pituitary Adenoma</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr"/>
+      <c r="C853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr"/>
+      <c r="F853" t="inlineStr"/>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23158937</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Dataset Title: Depth-dependent phase evolution and multicomponent nitride formation during plasma nitriding of a Zr-Ti-Nb-Al compositionally complex alloy</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr"/>
+      <c r="C854" t="inlineStr"/>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr"/>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23204463</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>X-ray Pair DIstribution Function dataset: Local Structure and Dynamics of Three-Dimensional Covalent Organic Frameworks</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr"/>
+      <c r="C855" t="inlineStr"/>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr"/>
+      <c r="F855" t="inlineStr"/>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21998650</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>NU-Kazakhstan 2026: YOLOv8n-seg polyp segmentation model for the Endoscopy Trainer</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr"/>
+      <c r="C856" t="inlineStr"/>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr"/>
+      <c r="F856" t="inlineStr"/>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23196636</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Mouse Brain Microscopy Dataset for 3D-GUSL</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr"/>
+      <c r="C857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr"/>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23201343</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Bright-Field Microscopy Dataset of Fungal Filament Networks for Detection, Focus Modeling, and 3D Reconstruction</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr"/>
+      <c r="C858" t="inlineStr"/>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr"/>
+      <c r="F858" t="inlineStr"/>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23135747</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Histopathology image collection (30 images) - on-chain provenance record (MIAMA Chain #3)</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr"/>
+      <c r="C859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr"/>
+      <c r="F859" t="inlineStr"/>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23203789</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Explainable AI framework for skin lesion imaging based cancer detection.</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr"/>
+      <c r="C860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr"/>
+      <c r="F860" t="inlineStr"/>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13641363/</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>MLSC-BEDLUS-741-Annotations</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr"/>
+      <c r="C861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr"/>
+      <c r="F861" t="inlineStr"/>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/HFTV7D</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>MLSC-BEDSBO-490-Annotations</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr"/>
+      <c r="C862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr"/>
+      <c r="F862" t="inlineStr"/>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/VEBLGF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G862"/>
+  <dimension ref="A1:G997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18535,6 +18535,2841 @@
         </is>
       </c>
     </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>ProstateX MRI Image and Mask Dataset</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr"/>
+      <c r="C863" t="inlineStr"/>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr"/>
+      <c r="F863" t="inlineStr"/>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ajithdari/prostatex-mri-image-and-mask-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Brain Tumor MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr"/>
+      <c r="C864" t="inlineStr"/>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr"/>
+      <c r="F864" t="inlineStr"/>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nmkkjj/brain-tumor-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>CT Scans</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr"/>
+      <c r="C865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr"/>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/huntrxd/ct-scans</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>AstroVision: 3D Asteroid &amp; Photometry Dataset</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr"/>
+      <c r="C866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr"/>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/hassaanfazal/astrovision-3d-asteroid-and-photometry-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Retina OCT CFP Images</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr"/>
+      <c r="C867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr"/>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ajithdari/retina-oct-cfp-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>CPD1K: A Colon Polyp Segmentation Dataset</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr"/>
+      <c r="C868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr"/>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/haoranyang20030523/cpd1k-a-colon-polyp-segmentation-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>DISEASE IDENTIFICATION AND RETINAL FUNDUS SCAN.</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr"/>
+      <c r="C869" t="inlineStr"/>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr"/>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/acharyakamal/disease-identification-and-retinal-fundus-scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>HAM10000 Skin Lesion Object Detection (YOLO)</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr"/>
+      <c r="C870" t="inlineStr"/>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr"/>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rizkyxp/ham10000-object-detection-yolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>theshoaibme/panorgan-ultrasound-nerve-segmentation</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr"/>
+      <c r="C871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/theshoaibme/panorgan-ultrasound-nerve-segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>THE EFFECTIVENESS OF NEURAL NETWORKS AND ARTIFICIAL INTELLIGENCE ALGORITHMS IN THE EARLY DETECTION OF TUBERCULOSIS ON CHEST X-RAYS AND COMPUTED TOMOGRAPHY IMAGES</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr"/>
+      <c r="C872" t="inlineStr"/>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23220340</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-HNSC collection</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr"/>
+      <c r="C873" t="inlineStr"/>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr"/>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837368</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Experimental dataset for time–temperature effects on the tempering response of AISI 4340 steel</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr"/>
+      <c r="C874" t="inlineStr"/>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23215479</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>CoSAXS example dataset - ptychography on siemens star</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr"/>
+      <c r="C875" t="inlineStr"/>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23210803</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the HTAN-VANDERBILT collection</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr"/>
+      <c r="C876" t="inlineStr"/>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr"/>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837342</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>HTAN-TNP-SARDANA: DICOM converted cyclic immunofluorescence and H&amp;E whole slide images from the HTAN SARDANA Trans-Network Project</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr"/>
+      <c r="C877" t="inlineStr"/>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837341</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-UVM collection</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr"/>
+      <c r="C878" t="inlineStr"/>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837091</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-READ collection</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr"/>
+      <c r="C879" t="inlineStr"/>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837399</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-PRAD collection</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr"/>
+      <c r="C880" t="inlineStr"/>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837396</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-PCPG collection</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr"/>
+      <c r="C881" t="inlineStr"/>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837393</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-PAAD collection</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr"/>
+      <c r="C882" t="inlineStr"/>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837392</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-OV collection</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr"/>
+      <c r="C883" t="inlineStr"/>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837387</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-MESO collection</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr"/>
+      <c r="C884" t="inlineStr"/>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr"/>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837386</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-LUSC collection</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr"/>
+      <c r="C885" t="inlineStr"/>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr"/>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837384</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-LUAD collection</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr"/>
+      <c r="C886" t="inlineStr"/>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr"/>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837383</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-LIHC collection</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr"/>
+      <c r="C887" t="inlineStr"/>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837382</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-LGG collection</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr"/>
+      <c r="C888" t="inlineStr"/>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837379</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-KIRP collection</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr"/>
+      <c r="C889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837377</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-KIRC collection</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr"/>
+      <c r="C890" t="inlineStr"/>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837374</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-KICH collection</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr"/>
+      <c r="C891" t="inlineStr"/>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837371</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-GBM collection</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr"/>
+      <c r="C892" t="inlineStr"/>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr"/>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837367</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-ESCA collection</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr"/>
+      <c r="C893" t="inlineStr"/>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr"/>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837365</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-DLBC collection</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr"/>
+      <c r="C894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr"/>
+      <c r="F894" t="inlineStr"/>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837360</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-COAD collection</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr"/>
+      <c r="C895" t="inlineStr"/>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr"/>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837359</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-CHOL collection</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr"/>
+      <c r="C896" t="inlineStr"/>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837175</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-CESC collection</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr"/>
+      <c r="C897" t="inlineStr"/>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837357</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-BRCA collection</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr"/>
+      <c r="C898" t="inlineStr"/>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr"/>
+      <c r="F898" t="inlineStr"/>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837352</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-BLCA collection</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr"/>
+      <c r="C899" t="inlineStr"/>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr"/>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837349</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the TCGA-ACC collection</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr"/>
+      <c r="C900" t="inlineStr"/>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr"/>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837348</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>DICOM converted whole slide hematoxylin and eosin images of rhabdomyosarcoma from Children's Oncology Group trials</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr"/>
+      <c r="C901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr"/>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837347</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the ICDC-Glioma collection</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr"/>
+      <c r="C902" t="inlineStr"/>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr"/>
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837345</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the CPTAC-UCEC collection</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr"/>
+      <c r="C903" t="inlineStr"/>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837338</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the CPTAC-SAR collection</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr"/>
+      <c r="C904" t="inlineStr"/>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837334</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the CPTAC-LUAD collection</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr"/>
+      <c r="C905" t="inlineStr"/>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837330</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the CPTAC-CM collection</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr"/>
+      <c r="C906" t="inlineStr"/>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837324</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>DICOM converted Slide Microscopy images for the CPTAC-BRCA collection</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr"/>
+      <c r="C907" t="inlineStr"/>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837323</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Pan-Cancer-Nuclei-Seg-DICOM: DICOM converted Dataset of Segmented Nuclei in Hematoxylin and Eosin Stained Histopathology Images</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr"/>
+      <c r="C908" t="inlineStr"/>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22818207</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>CCDI-MCI: DICOM converted whole slide hematoxylin and eosin stained images from the Molecular Characterization Initiative of the National Cancer Institute's Childhood Cancer Data Initiative</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr"/>
+      <c r="C909" t="inlineStr"/>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/18675667</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>HCMI-CMDC: DICOM converted whole slide images from the Human Cancer Models Initiative (HCMI) Cancer Model Development Center (CMDC)</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr"/>
+      <c r="C910" t="inlineStr"/>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837339</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>CGCI-HTMCP-LC: DICOM converted whole slide images from the Cancer Genome Characterization Initiative (CGCI) HIV+ Tumor Molecular Characterization Project (HTMCP) - Lung Cancer</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr"/>
+      <c r="C911" t="inlineStr"/>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837320</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>CGCI-HTMCP-DLBCL: DICOM converted whole slide images from the Cancer Genome Characterization Initiative (CGCI) HIV+ Tumor Molecular Characterization Project (HTMCP) - Diffuse Large B-Cell Lymphoma</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr"/>
+      <c r="C912" t="inlineStr"/>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr"/>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837317</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>CGCI-HTMCP-CC: DICOM converted whole slide images from the Cancer Genome Characterization Initiative (CGCI) HIV+ Tumor Molecular Characterization Project (HTMCP) - Cervical Cancer</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr"/>
+      <c r="C913" t="inlineStr"/>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837314</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>CGCI-BLGSP: DICOM converted whole slide images from the Cancer Genome Characterization Initiative (CGCI) - Burkitt Lymphoma Genome Sequencing Project (BLGSP)</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr"/>
+      <c r="C914" t="inlineStr"/>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr"/>
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837313</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>CDDP-EAGLE-1: DICOM converted whole slide images from the Environment And Genetics in Lung cancer Etiology (EAGLE) study</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr"/>
+      <c r="C915" t="inlineStr"/>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22837312</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>BoneMarrowWSI-PediatricLeukemia: A Comprehensive Dataset of Bone Marrow Aspirate Smear Whole Slide Images with Expert Annotations and Clinical Data in Pediatric Leukemia</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr"/>
+      <c r="C916" t="inlineStr"/>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22818005</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Skin Lesion and Healthy Skin Dataset for 4-Class Object Detection (YOLO annotation)</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr"/>
+      <c r="C917" t="inlineStr"/>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr"/>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23223193</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Coronary artery calcium score and acute myocardial infarction in young Bangladeshi adults: a case-control study</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr"/>
+      <c r="C918" t="inlineStr"/>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/9FOIQR</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Developing a Practical Primary Care POCUS Curriculum for Academic Primary Care Clinicians</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr"/>
+      <c r="C919" t="inlineStr"/>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>POCUS</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/OBERSB</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Ankle MRI for Anterolateral Soft Tissue Impingement: Increased Accuracy with the Use of Contrast-Enhanced Fat-Suppressed 3D-FSPGR MRI</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr"/>
+      <c r="C920" t="inlineStr"/>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/254/2627205/PMC2627205_kjr-9-409-g005.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>An objective measure of response on whole-body MRI in metastatic hormone sensitive prostate cancer treated with androgen deprivation therapy, external beam radiotherapy, and radium-223</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr"/>
+      <c r="C921" t="inlineStr"/>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/243/11027342/PMC11027342_tqae005f1.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Predicting cytogenetic risk in multiple myeloma using conventional whole-body MRI, spinal dynamic contrast-enhanced MRI, and spinal diffusion-weighted imaging</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr"/>
+      <c r="C922" t="inlineStr"/>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/390/11006637/PMC11006637_13244_2024_1672_Fig6_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Improving Diagnostic Performance of MRI for Temporal Lobe Epilepsy With Deep Learning-Based Image Reconstruction in Patients With Suspected Focal Epilepsy</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr"/>
+      <c r="C923" t="inlineStr"/>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/375/10973740/PMC10973740_kjr-25-374-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Clinical and neuroradiological approach to fucosidosis in a child with atypical presentation</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr"/>
+      <c r="C924" t="inlineStr"/>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/215/4683895/PMC4683895_AIAN-18-471-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Clinical evaluation of 4D MRI in the delineation of gross and internal tumor volumes in comparison with 4DCT</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr"/>
+      <c r="C925" t="inlineStr"/>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>dMRI</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/85/6753727/PMC6753727_ACM2-20-51-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Surgical Outcomes of Thalamic Tumors in Children: The Importance of Diffusion Tensor Imaging, Neuro-Navigation and Intraoperative Neurophysiological Monitoring</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr"/>
+      <c r="C926" t="inlineStr"/>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/400/6212692/PMC6212692_btrt-6-60-g003.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>SP-DTI: subpocket-informed transformer for drug–target interaction prediction</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr"/>
+      <c r="C927" t="inlineStr"/>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="inlineStr"/>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/337/11886779/PMC11886779_btaf011f4.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Diffusion Tensor Magnetic Resonance Imaging Strategies for Color Mapping of Human Brain Anatomy</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr"/>
+      <c r="C928" t="inlineStr"/>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr"/>
+      <c r="F928" t="inlineStr"/>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/356/5992900/PMC5992900_JMSS-8-73-g016.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Whole heart 3 D MR coronary angiography with and without extracellular contrast agent</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr"/>
+      <c r="C929" t="inlineStr"/>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Echocardiography</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/21/7852002/PMC7852002_12968_2009_Article_758_Fig1_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>ECG-gated MR angiography at 3T for follow-up after surgery involving the ascending aorta</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr"/>
+      <c r="C930" t="inlineStr"/>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>MR Angiography</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/162/10237692/PMC10237692_medi-102-e33864-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Characteristics of Posterior Ethmoidal Artery and Its Relationship with Anterior Ethmoidal Artery and Skull Base on CT Scan</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr"/>
+      <c r="C931" t="inlineStr"/>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr"/>
+      <c r="F931" t="inlineStr"/>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/212/11572270/PMC11572270_MedeniMedJ-39-85-figure-7.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Examining the Relationship between Salivary Amylase Level, Head Trauma Severity and CT Scan Results in Patients with Isolated Mild Head Trauma</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr"/>
+      <c r="C932" t="inlineStr"/>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr"/>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/279/9008343/PMC9008343_bet-10-59-g003.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Relationship of Oral Tumor Thickness with the rate of lymph node metastasis in Neck based on CT Scan</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr"/>
+      <c r="C933" t="inlineStr"/>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr"/>
+      <c r="F933" t="inlineStr"/>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/356/5432703/PMC5432703_PJMS-33-353-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Relapsed isolated CNS lymphoma treated with radiotherapy and intrathecal methotrexate followed by high ‐dose intravenous methotrexate, rituximab, and temozolomide: A case report</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr"/>
+      <c r="C934" t="inlineStr"/>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr"/>
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/148/10907348/PMC10907348_CCR3-12-e8409-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Mycosis fungoides staged by 18 F-flurodeoxyglucose positron emission tomography/computed tomography</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr"/>
+      <c r="C935" t="inlineStr"/>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr"/>
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/115/5106048/PMC5106048_medi-95-e5044-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Depiction of ventriculoperitoneal shunt obstruction with single-photon emission computed tomography/computed tomography</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr"/>
+      <c r="C936" t="inlineStr"/>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr"/>
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/234/4918499/PMC4918499_IJNM-31-246-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Gallbladder Visualization on Tc-99m-labeled Red Cell Scintigraphy: A Rare Finding with an Emphasis on Role of Single-photon Emission Computed Tomography/Computed Tomography</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr"/>
+      <c r="C937" t="inlineStr"/>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/355/5482025/PMC5482025_IJNM-32-233-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Beneath the surface: a case report on nonencapsulated Streptococcus pneumoniae -associated invasive disease in an immunocompromised patient</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr"/>
+      <c r="C938" t="inlineStr"/>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/338/10928390/PMC10928390_acmi-6-743.v3-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Delayed progressive haematoma after Le Fort I osteotomy: A possible severe complication in orthognatic surgery</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr"/>
+      <c r="C939" t="inlineStr"/>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/177/3692184/PMC3692184_DRJ-9-246-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Volumetric computed tomography with carbon nanotube X-ray source array for improved image quality and accuracy</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr"/>
+      <c r="C940" t="inlineStr"/>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>CBCT</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/95/10955816/PMC10955816_44172_2023_123_Fig6_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Micro-CT evaluation of the presence of voids in endodonticobturation</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr"/>
+      <c r="C941" t="inlineStr"/>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/224/11277948/PMC11277948_1852-4834-37-1-3-g001A.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Mapping disparities in access to lecanemab in Georgia</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr"/>
+      <c r="C942" t="inlineStr"/>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr"/>
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/334/12004269/PMC12004269_ALZ-21-e70100-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>The impact of 18-fluorodeoxyglucose positron emission tomography on the staging, management and outcome of anal cancer</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr"/>
+      <c r="C943" t="inlineStr"/>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr"/>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/334/2653751/PMC2653751_6604897f2.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>FDG-PET/CT lymph node staging after neoadjuvant chemotherapy in patients with adenocarcinoma of the esophageal –gastric junction</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr"/>
+      <c r="C944" t="inlineStr"/>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="inlineStr"/>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/390/5059406/PMC5059406_261_2016_820_Fig1_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>FDG-PET of Takayasu’s Arteritis</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr"/>
+      <c r="C945" t="inlineStr"/>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>FDG-PET</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr"/>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/18/4061346/PMC4061346_11606_2013_2695_Fig2_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Misinterpretation of an inflammatory FDG uptake in a patient treated for Hodgkin lymphoma: a case report</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr"/>
+      <c r="C946" t="inlineStr"/>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr"/>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/96/10261686/PMC10261686_AOJNMB-02-171-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Single-direction VATS left lower lobectomy and lymph node dissection after neoadjuvant chemotherapy combined with immunotherapy: a case report</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr"/>
+      <c r="C947" t="inlineStr"/>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr"/>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/95/8182500/PMC8182500_jtd-13-05-3182-f2.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Common Infections Following Lung Transplantation</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr"/>
+      <c r="C948" t="inlineStr"/>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/119/7121478/PMC7121478_437606_1_En_15_Fig9_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>PET-MRI tracking of imaging-visible microencapsulated stem cells in immunocompetent rabbits</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr"/>
+      <c r="C949" t="inlineStr"/>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr"/>
+      <c r="F949" t="inlineStr"/>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/83/3559359/PMC3559359_1532-429X-15-S1-M1-1.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Projection-Angle-Sensor-Assisted X-ray Computed Tomography for Cylindrical Lithium-Ion Batteries</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr"/>
+      <c r="C950" t="inlineStr"/>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="inlineStr"/>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/11/10892775/PMC10892775_sensors-24-01102-g004.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Diagnostic Value of Extraoral Periapical Radiograph in Comparison to Intraoral Periapical Radiograph: A Cross-sectional, Institutional Study</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr"/>
+      <c r="C951" t="inlineStr"/>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr"/>
+      <c r="F951" t="inlineStr"/>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/347/6104369/PMC6104369_CCD-9-406-g008.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>The Abdominal Radiograph</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr"/>
+      <c r="C952" t="inlineStr"/>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr"/>
+      <c r="F952" t="inlineStr"/>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/51/3913410/PMC3913410_umj0082-0179-f1a.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Determination of sexual dimorphism in humans by measurements of mandible on digital panoramic radiograph</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr"/>
+      <c r="C953" t="inlineStr"/>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr"/>
+      <c r="F953" t="inlineStr"/>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/32/5141654/PMC5141654_CCD-7-434-g004.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Low-dose pulsed vs standard pulsed fluoroscopy during ERCP to reduce radiation without change in image quality: Prospective randomized study</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr"/>
+      <c r="C954" t="inlineStr"/>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Fluoroscopy</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr"/>
+      <c r="F954" t="inlineStr"/>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/112/11018389/PMC11018389_10-1055-a-2284-8656_22879294.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Comparative analysis of automated breast volume scanner (ABVS) combined with conventional hand-held ultrasound and mammography in female breast cancer detection</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr"/>
+      <c r="C955" t="inlineStr"/>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr"/>
+      <c r="F955" t="inlineStr"/>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/393/10783283/PMC10783283_ms9-86-159-g005.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Multimodal deep learning for breast tumor classification: Integrating mammography and ultrasound for enhanced diagnostic accuracy</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr"/>
+      <c r="C956" t="inlineStr"/>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr"/>
+      <c r="F956" t="inlineStr"/>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/258/12813411/PMC12813411_ACM2-27-e70464-g005.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Muscle Ultrasound Abnormalities in Individuals with RYR1 -Related Malignant Hyperthermia Susceptibility</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr"/>
+      <c r="C957" t="inlineStr"/>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr"/>
+      <c r="F957" t="inlineStr"/>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/143/10357171/PMC10357171_jnd-10-jnd230018-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Comparative study between bowel ultrasound and magnetic resonance enterography among Egyptian inflammatory bowel disease patients</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr"/>
+      <c r="C958" t="inlineStr"/>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr"/>
+      <c r="F958" t="inlineStr"/>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/49/7579751/PMC7579751_WJG-26-5884-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Evaluation of clinical effect of transabdominal sonography and transvaginal sonography in early diagnosis of ectopic gestation</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr"/>
+      <c r="C959" t="inlineStr"/>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr"/>
+      <c r="F959" t="inlineStr"/>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/142/5368329/PMC5368329_PJMS-33-53-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Brain sonography in African infants with complicated sporadic bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr"/>
+      <c r="C960" t="inlineStr"/>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr"/>
+      <c r="F960" t="inlineStr"/>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/349/3883232/PMC3883232_NMJ-54-320-g006.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Comprehensive echocardiographic imaging of atrioventricular valves in children with atrioventricular septal defect: Accuracy of 2D and 3D imaging and reasons for disagreement</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr"/>
+      <c r="C961" t="inlineStr"/>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Echocardiography</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr"/>
+      <c r="F961" t="inlineStr"/>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/215/6528495/PMC6528495_AJC-21-214-g005.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Handheld contact-type OCT and color fundus system forretinal imaging</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr"/>
+      <c r="C962" t="inlineStr"/>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr"/>
+      <c r="F962" t="inlineStr"/>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/221/11019701/PMC11019701_boe-15-4-2681-g009.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>SD-OCT and Adaptive Optics Imaging of Outer Retinal Tubulation</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr"/>
+      <c r="C963" t="inlineStr"/>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>SD-OCT</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr"/>
+      <c r="F963" t="inlineStr"/>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/186/5321857/PMC5321857_opx-94-411-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Macular Surgery Using Intraoperative Spectral Domain Optical Coherence Tomography</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr"/>
+      <c r="C964" t="inlineStr"/>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>SD-OCT</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr"/>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/378/4687266/PMC4687266_JOVR-10-309-g007.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Mutational Profile and Retinal Phenotypes of PCARE -Related Cone-Rod Dystrophies in a Mexican Cohort</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr"/>
+      <c r="C965" t="inlineStr"/>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>SD-OCT</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr"/>
+      <c r="F965" t="inlineStr"/>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/88/10927338/PMC10927338_JOPH2024-4003914.001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Swept-source optical coherence tomography features of regressed macular retinoblastoma</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr"/>
+      <c r="C966" t="inlineStr"/>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr"/>
+      <c r="F966" t="inlineStr"/>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/164/6896562/PMC6896562_IJO-67-2013-g004.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>SS-OCT/OCTA Assessment of Choroidal Structure in Vitreoretinal Lymphoma Patients and Their Changes During Intravitreal Methotrexate Chemotherapy</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr"/>
+      <c r="C967" t="inlineStr"/>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr"/>
+      <c r="F967" t="inlineStr"/>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/32/12534891/PMC12534891_tvst-14-10-25-f001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Nonperfused Retinal Capillaries—A New Method Developed on OCT and OCTA</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr"/>
+      <c r="C968" t="inlineStr"/>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>OCTA</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr"/>
+      <c r="F968" t="inlineStr"/>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/20/11993128/PMC11993128_iovs-66-4-22-f001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>The scientific progress and prospects of artificial intelligence in digestive endoscopy: A comprehensive bibliometric analysis</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr"/>
+      <c r="C969" t="inlineStr"/>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr"/>
+      <c r="F969" t="inlineStr"/>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/323/9704924/PMC9704924_medi-101-e31931-g005.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Recent advances in diagnostic upper endoscopy</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr"/>
+      <c r="C970" t="inlineStr"/>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr"/>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/245/7002908/PMC7002908_WJG-26-433-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Diaphragmatic hernia as a rare complication of colonoscopy</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr"/>
+      <c r="C971" t="inlineStr"/>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr"/>
+      <c r="F971" t="inlineStr"/>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/161/5779774/PMC5779774_medi-97-e9660-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Abnormal Colorectal Cancer Test Follow-Up: A Quality Improvement Initiative at a Federally Qualified Health Center</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr"/>
+      <c r="C972" t="inlineStr"/>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Colonoscopy</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr"/>
+      <c r="F972" t="inlineStr"/>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/62/10981848/PMC10981848_10.1177_21501319241242571-fig2.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Do Basic Psychomotor Skills Transfer Between Different Image-based Procedures?</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr"/>
+      <c r="C973" t="inlineStr"/>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Colonoscopy</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr"/>
+      <c r="F973" t="inlineStr"/>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/26/2848730/PMC2848730_268_2010_432_Fig2_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Competition in Colon Cancer Screening? What Is the Role of Colonoscopy?</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr"/>
+      <c r="C974" t="inlineStr"/>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr"/>
+      <c r="F974" t="inlineStr"/>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/149/4513805/PMC4513805_vim-0030-0018-g05.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Endoscopic repair of spontaneous esophageal rupture during gastroscopy</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr"/>
+      <c r="C975" t="inlineStr"/>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr"/>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/322/6283190/PMC6283190_medi-97-e13422-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Sodium Fluorescein for Ureteral Jet Detection: A Prospective Observational Study</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr"/>
+      <c r="C976" t="inlineStr"/>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Laparoscopy</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr"/>
+      <c r="F976" t="inlineStr"/>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/29/6191068/PMC6191068_jls0201637180001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>High-grade undifferentiated pleomorphic sarcoma of the pelvis: A case report and review of literature</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr"/>
+      <c r="C977" t="inlineStr"/>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr"/>
+      <c r="F977" t="inlineStr"/>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/307/4944637/PMC4944637_UA-8-372-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Inflammatory Septal Nasal Polyp</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr"/>
+      <c r="C978" t="inlineStr"/>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Rhinoscopy</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr"/>
+      <c r="F978" t="inlineStr"/>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/339/4710886/PMC4710886_ijo-27-319-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Service Quality and Residents’ Preferences for Facilitated Self-Service Fundus Disease Screening: Cross-Sectional Study</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr"/>
+      <c r="C979" t="inlineStr"/>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr"/>
+      <c r="F979" t="inlineStr"/>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/298/11063888/PMC11063888_jmir_v26i1e45545_fig2.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Correction Method for Optical Scaling of Fundoscopy Images: Development, Validation, and First Implementation</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr"/>
+      <c r="C980" t="inlineStr"/>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr"/>
+      <c r="F980" t="inlineStr"/>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/394/10829800/PMC10829800_iovs-65-1-43-f001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Refined image quality assessment for color fundus photography based on deep learning</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr"/>
+      <c r="C981" t="inlineStr"/>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Color Fundus</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr"/>
+      <c r="F981" t="inlineStr"/>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/3/10903193/PMC10903193_10.1177_20552076231207582-fig3.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Delayed suprachoroidal hemorrhage after cataract surgery</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr"/>
+      <c r="C982" t="inlineStr"/>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr"/>
+      <c r="F982" t="inlineStr"/>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/262/5943884/PMC5943884_medi-97-e8697-g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Anterior ischemic optic neuropathy in a patient with optic disc Drusen while on FOLFOX Chemotherapy for colon cancer: the value of Occam ’s Razor and Hickam’s dictum</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr"/>
+      <c r="C983" t="inlineStr"/>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr"/>
+      <c r="F983" t="inlineStr"/>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/9/6626935/PMC6626935_RomJOphthalmol-63-174-g003.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Multimodal imaging study of lipemia retinalis with diabetic retinopathy: A case report</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr"/>
+      <c r="C984" t="inlineStr"/>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>OCTA</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr"/>
+      <c r="F984" t="inlineStr"/>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/94/9294873/PMC9294873_WJCC-10-6736-g004.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Candida endophthalmitis and Candida pneumonia after trans‐urethral lithotripsy: A case report</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr"/>
+      <c r="C985" t="inlineStr"/>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr"/>
+      <c r="F985" t="inlineStr"/>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/18/11004260/PMC11004260_CCR3-12-e8746-g003.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Open Fundus Photograph Dataset with Pathologic Myopia Recognition and Anatomical Structure Annotation</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr"/>
+      <c r="C986" t="inlineStr"/>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr"/>
+      <c r="F986" t="inlineStr"/>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/113/10799845/PMC10799845_41597_2024_2911_Fig2_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Dermoscopic, Histological, Confocal Microscopy Correlation of Atypical-Dysplastic Melanocytic Nevi</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr"/>
+      <c r="C987" t="inlineStr"/>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Confocal Microscopy</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr"/>
+      <c r="F987" t="inlineStr"/>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/177/10868881/PMC10868881_dp1401a36g001.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Reflectance confocal microscopy of tinea nigra: comparing images withdermoscopy and mycological examination results *</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr"/>
+      <c r="C988" t="inlineStr"/>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Confocal Microscopy</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr"/>
+      <c r="F988" t="inlineStr"/>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/60/5595614/PMC5595614_abd-92-04-0568-g04.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Generative artificial intelligence as an aid in interpreting thyroid FNA cytopathological images: Are we there yet?</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr"/>
+      <c r="C989" t="inlineStr"/>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Cytopathology</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr"/>
+      <c r="F989" t="inlineStr"/>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/298/12723627/PMC12723627_CNCY-134-0-g003.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>PATHOLOGY VISIONS 2019</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr"/>
+      <c r="C990" t="inlineStr"/>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr"/>
+      <c r="F990" t="inlineStr"/>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/92/7003557/PMC7003557_JPI-11-1-g010.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>The slow-paced digital evolution of pathology: lights and shadows from a multifaceted board</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr"/>
+      <c r="C991" t="inlineStr"/>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr"/>
+      <c r="F991" t="inlineStr"/>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/96/10462988/PMC10462988_pathol-2023-03-127-g003.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Review of immunohistochemical typing of endometrial carcinoma at the Lagos University Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr"/>
+      <c r="C992" t="inlineStr"/>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr"/>
+      <c r="F992" t="inlineStr"/>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/344/7040300/PMC7040300_AFHS1903-2468Fig2.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>An Incidental Diagnosis of Extraosseous Ewing’s Sarcoma in the Kidney</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr"/>
+      <c r="C993" t="inlineStr"/>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr"/>
+      <c r="F993" t="inlineStr"/>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/339/10924782/PMC10924782_cureus-0016-00000053916-i07.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Early Detection of Monopolar Radiofrequency Tip Rupture Using Polarized Dermoscopy: A Preventive Approach Against Treatment ‐Related Burns</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr"/>
+      <c r="C994" t="inlineStr"/>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr"/>
+      <c r="F994" t="inlineStr"/>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/29/12813583/PMC12813583_JOCD-25-e70678-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Invisible Lichen Planopilaris Unmasked by Dermatoscopy</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr"/>
+      <c r="C995" t="inlineStr"/>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr"/>
+      <c r="F995" t="inlineStr"/>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/269/5551312/PMC5551312_IJT-9-76-g003.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Applications of Ultraviolet and Sub-ultraviolet Dermatoscopy in Neoplastic and Non-neoplastic Dermatoses: A Systematic Review</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr"/>
+      <c r="C996" t="inlineStr"/>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr"/>
+      <c r="F996" t="inlineStr"/>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/231/10890990/PMC10890990_13555_2024_1104_Fig22_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Diagnosis of Trombiculosis by Videodermatoscopy</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr"/>
+      <c r="C997" t="inlineStr"/>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr"/>
+      <c r="F997" t="inlineStr"/>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/318/4036784/PMC4036784_13-0767-F.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G997"/>
+  <dimension ref="A1:G1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21370,6 +21370,111 @@
         </is>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Dataset related to "Patient-reported acceptability of multiparametric renal MRI: a multicentre study"</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr"/>
+      <c r="C998" t="inlineStr"/>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr"/>
+      <c r="F998" t="inlineStr"/>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23038142</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>ACR CT Accreditation Phantom Scans: FPH and FPB Formats</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr"/>
+      <c r="C999" t="inlineStr"/>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr"/>
+      <c r="F999" t="inlineStr"/>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23072038</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Awakening ImageCAS: Coronary Ostium and Centerline annotations for the ImageCAS CCTA Dataset</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr"/>
+      <c r="C1000" t="inlineStr"/>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr"/>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23243094</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Dataset related to article: MICROSTRUCTURAL ALTERATION OF THE FRONTAL ASLANT TRACT IN TOURETTE SYNDROME</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr"/>
+      <c r="C1001" t="inlineStr"/>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr"/>
+      <c r="F1001" t="inlineStr"/>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23242894</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>RCTE: A multi-class object detection framework for dental panoramic radiographs.</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr"/>
+      <c r="C1002" t="inlineStr"/>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr"/>
+      <c r="F1002" t="inlineStr"/>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13649147/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1002"/>
+  <dimension ref="A1:G1008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21475,6 +21475,132 @@
         </is>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Creutzfeldt–Jakob Disease 60K Dataset</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr"/>
+      <c r="C1003" t="inlineStr"/>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr"/>
+      <c r="F1003" t="inlineStr"/>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/gowtha69/creutzfeldtjakob-disease-60k-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>brain tumor MRI classification</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr"/>
+      <c r="C1004" t="inlineStr"/>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr"/>
+      <c r="F1004" t="inlineStr"/>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/iqranisa1122/brain-tumor-mri-classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Ovarian Cancer Risk &amp; Detection Dataset</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr"/>
+      <c r="C1005" t="inlineStr"/>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr"/>
+      <c r="F1005" t="inlineStr"/>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/gowtha69/ovarian-cancer-risk-and-detection-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>GeoShift: a four-survey geochemical benchmark for cross-survey evaluation under detection-limit censoring (data)</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr"/>
+      <c r="C1006" t="inlineStr"/>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr"/>
+      <c r="F1006" t="inlineStr"/>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23269887</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>SoftiMAX example dataset - ptychography on siemens star</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr"/>
+      <c r="C1007" t="inlineStr"/>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr"/>
+      <c r="F1007" t="inlineStr"/>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23246616</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Global-to-local image quality assessment in optical microscopy via fast deep learning predictions - Supporting Data</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr"/>
+      <c r="C1008" t="inlineStr"/>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr"/>
+      <c r="F1008" t="inlineStr"/>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/17184938</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1008"/>
+  <dimension ref="A1:G1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21601,6 +21601,27 @@
         </is>
       </c>
     </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Brain Tumor MRI Dataset 1</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr"/>
+      <c r="C1009" t="inlineStr"/>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr"/>
+      <c r="F1009" t="inlineStr"/>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nmkkjj/brain-tumor-mri-dataset-1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1009"/>
+  <dimension ref="A1:G1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21622,6 +21622,111 @@
         </is>
       </c>
     </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Trending Movies - Dataset</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr"/>
+      <c r="C1010" t="inlineStr"/>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr"/>
+      <c r="F1010" t="inlineStr"/>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sidkoth90/trending-movies-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Udaysah172/pmram-bangladeshi-brain-cancer-mri-dataset-raw</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr"/>
+      <c r="C1011" t="inlineStr"/>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr"/>
+      <c r="F1011" t="inlineStr"/>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/Udaysah172/pmram-bangladeshi-brain-cancer-mri-dataset-raw</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Dataset for the publication "Gold Single-Atom Catalysts Enable Selective Shuttle Hydrochlorination of Alkynes"</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr"/>
+      <c r="C1012" t="inlineStr"/>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr"/>
+      <c r="F1012" t="inlineStr"/>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/20426024</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Dataset of "Potential-induced surface evolution of Pt–Rh alloy electrocatalysts"</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr"/>
+      <c r="C1013" t="inlineStr"/>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr"/>
+      <c r="F1013" t="inlineStr"/>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23314975</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>CellVFL dataset</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr"/>
+      <c r="C1014" t="inlineStr"/>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr"/>
+      <c r="F1014" t="inlineStr"/>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23308087</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1014"/>
+  <dimension ref="A1:G1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21727,6 +21727,153 @@
         </is>
       </c>
     </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>alzheimer-mri-4-class-dataset</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr"/>
+      <c r="C1015" t="inlineStr"/>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr"/>
+      <c r="F1015" t="inlineStr"/>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sanjustrisg/alzheimer-mri-4-class-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Digital Knee X-ray Images</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr"/>
+      <c r="C1016" t="inlineStr"/>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr"/>
+      <c r="F1016" t="inlineStr"/>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/vyshuss/digital-knee-x-ray-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Veterinary Health Dataset</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr"/>
+      <c r="C1017" t="inlineStr"/>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr"/>
+      <c r="F1017" t="inlineStr"/>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/blaineee/veterinary-health-and-parasitology-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>4D Dataset of a Commercial 21700 Lithium-Ion Battery Acquired Using Energy-Dispersive X-ray Diffraction Tomography (EDDT)</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr"/>
+      <c r="C1018" t="inlineStr"/>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr"/>
+      <c r="F1018" t="inlineStr"/>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23321071</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Dataset of a Cross-Section of a Commercial 21700 Lithium-Ion Battery Acquired Using Energy-Dispersive X-ray Diffraction Tomography (EDDT)</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr"/>
+      <c r="C1019" t="inlineStr"/>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr"/>
+      <c r="F1019" t="inlineStr"/>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23320488</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Skin Lesion and Healthy Skin Dataset for 4-Class Object Detection (YOLO annotation)</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr"/>
+      <c r="C1020" t="inlineStr"/>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr"/>
+      <c r="F1020" t="inlineStr"/>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23323823</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>ReViT-RF: A hybrid ResNet-50-Vision Transformer with a Radiomic Feature Fusion framework for lung tumor classification and TNM-based stage prediction using CT images.</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr"/>
+      <c r="C1021" t="inlineStr"/>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr"/>
+      <c r="F1021" t="inlineStr"/>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13657286/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1021"/>
+  <dimension ref="A1:G1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21874,6 +21874,69 @@
         </is>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Beach Sand Geochemical Dataset (Emilia-Romagna Coast, Italy) — 2006 and 2020 monitoring campaigns</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr"/>
+      <c r="C1022" t="inlineStr"/>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr"/>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22256074</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Data for "GENIE: a multi-agent system for closed-loop autonomous microscopy": raw images, analysis results and verification tables</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr"/>
+      <c r="C1023" t="inlineStr"/>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr"/>
+      <c r="F1023" t="inlineStr"/>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23245979</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Dataset for article titled: Annular Erosion Footprint under Static Ultrasonic Pulsating Water Jet Exposure</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr"/>
+      <c r="C1024" t="inlineStr"/>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr"/>
+      <c r="F1024" t="inlineStr"/>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21339043</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1024"/>
+  <dimension ref="A1:G1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21937,6 +21937,447 @@
         </is>
       </c>
     </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Mri Dataset Brain Vesel</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr"/>
+      <c r="C1025" t="inlineStr"/>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr"/>
+      <c r="F1025" t="inlineStr"/>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mahinbinmarfath/mri-dataset-brain-vesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Spinal MRI: Vertebral Lesion Detection Dataset</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr"/>
+      <c r="C1026" t="inlineStr"/>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr"/>
+      <c r="F1026" t="inlineStr"/>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/berkutayasan/spinal-mri-vertebral-lesion-detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>UFC Historical Fight Dataset (1993–2026)</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr"/>
+      <c r="C1027" t="inlineStr"/>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr"/>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/larissapavan/ufc-historical-fight-dataset-19942026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Multiplant Foliar Dataset</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr"/>
+      <c r="C1028" t="inlineStr"/>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr"/>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sarvesha223454/multiplant-foliar-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Dataset for "Arsenic behavior and release from mine tailings in tropical semiarid region: insights from geochemistry, mineralogy, and texture"</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr"/>
+      <c r="C1029" t="inlineStr"/>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr"/>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23389363</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Supplementary material to: Evaluability of archived anterior segment OCT images of canine corneal ulcers: a retrospective feasibility study</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr"/>
+      <c r="C1030" t="inlineStr"/>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr"/>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23375355</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Conditional-Augmentation-of-Esophageal-Endoscopy-Images</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr"/>
+      <c r="C1031" t="inlineStr"/>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Endoscopy</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr"/>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23371743</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0013 – Tribolium castaneum AGOC{FutschM'#O(NLS)-mTagBFP} #2 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr"/>
+      <c r="C1032" t="inlineStr"/>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr"/>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222953</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0012 – Tribolium castaneum AGOC{FutschM'#O(NLS)-mTagBFP} #2 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr"/>
+      <c r="C1033" t="inlineStr"/>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr"/>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222951</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0011 – Tribolium castaneum AGOC{FutschM'#O(NLS)-mTagBFP} #2 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr"/>
+      <c r="C1034" t="inlineStr"/>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr"/>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222941</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0010 – Tribolium castaneum AGOC{DistPebbled'#O(NLS)-mTagBFP} #1 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr"/>
+      <c r="C1035" t="inlineStr"/>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr"/>
+      <c r="F1035" t="inlineStr"/>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222933</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0009 – Tribolium castaneum AGOC{Ase'#O(NLS)-mTagBFP} #1 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr"/>
+      <c r="C1036" t="inlineStr"/>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr"/>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222913</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0008 – Tribolium castaneum AGOC{Ase'#O(NLS)-mTagBFP} #1 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr"/>
+      <c r="C1037" t="inlineStr"/>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr"/>
+      <c r="F1037" t="inlineStr"/>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222904</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0004 – Tribolium castaneum AGOC{ATub'#O(NLS)-mTagBFP} #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 1/2</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr"/>
+      <c r="C1038" t="inlineStr"/>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr"/>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222788</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0003 – Tribolium castaneum AGOC{ATub'#O(NLS)-mTagBFP} #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 2/2</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr"/>
+      <c r="C1039" t="inlineStr"/>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr"/>
+      <c r="F1039" t="inlineStr"/>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222775</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0003 – Tribolium castaneum AGOC{ATub'#O(NLS)-mTagBFP} #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 1/2</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr"/>
+      <c r="C1040" t="inlineStr"/>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr"/>
+      <c r="F1040" t="inlineStr"/>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222756</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0002 – Tribolium castaneum AGOC{ATub'#O(NLS)-mTagBFP} #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 2/2</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr"/>
+      <c r="C1041" t="inlineStr"/>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr"/>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222746</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0002 – Tribolium castaneum AGOC{ATub'#O(NLS)-mTagBFP} #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 1/2</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr"/>
+      <c r="C1042" t="inlineStr"/>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr"/>
+      <c r="F1042" t="inlineStr"/>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222734</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0001 – Tribolium castaneum AGOC{ATub'#O(NLS)-mTagBFP} #1 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 2/2</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr"/>
+      <c r="C1043" t="inlineStr"/>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr"/>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222703</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0001 – Tribolium castaneum AGOC{ATub'#O(NLS)-mTagBFP} #1 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 1/2</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr"/>
+      <c r="C1044" t="inlineStr"/>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr"/>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222678</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Leakage-controlled benchmark of deep learning transfer from web-scraped microorganism images to laboratory microscopy: manifests, lcbench protocol package, model predictions and results</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr"/>
+      <c r="C1045" t="inlineStr"/>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr"/>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23375941</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1045"/>
+  <dimension ref="A1:G1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22378,6 +22378,132 @@
         </is>
       </c>
     </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Dataset associated with "Intermittent gas-liquid rearrangement controls the mixing of gases in porous media"</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr"/>
+      <c r="C1046" t="inlineStr"/>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="inlineStr"/>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/19228235</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>Ongoing Solar Flare Peak Flux Nowcasting dataset</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr"/>
+      <c r="C1047" t="inlineStr"/>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr"/>
+      <c r="F1047" t="inlineStr"/>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23403057</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Dataset for publication: Flexible Supercapacitors based on TiO2 ALDcoated AC with ultra-long cycling stability</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr"/>
+      <c r="C1048" t="inlineStr"/>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr"/>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23394734</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>Brightfield microscopy images and single-cell morphology measurements of Saccharomyces cerevisiae and Schizosaccharomyces pombe</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr"/>
+      <c r="C1049" t="inlineStr"/>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr"/>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23377605</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (80-study corpus, manuscript v0.4.7)</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr"/>
+      <c r="C1050" t="inlineStr"/>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr"/>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23414031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Gilbert Family NF Type 1 Institute Research and Clinical Research Proposal</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr"/>
+      <c r="C1051" t="inlineStr"/>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr"/>
+      <c r="F1051" t="inlineStr"/>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn71998269</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1051"/>
+  <dimension ref="A1:G1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22504,6 +22504,132 @@
         </is>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>AD MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr"/>
+      <c r="C1052" t="inlineStr"/>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr"/>
+      <c r="F1052" t="inlineStr"/>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nagarajani21phd0001/ad-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>Dataset from: Trusting the Inverse, Reliability-Aware Mapping for Simulation-Based Microstructure Estimation in Diffusion MRI</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr"/>
+      <c r="C1053" t="inlineStr"/>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>dMRI</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr"/>
+      <c r="F1053" t="inlineStr"/>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23167328</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>Dataset related to the original article: Reuse of plastic waste in asphalt mixtures with residual porous aggregates</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr"/>
+      <c r="C1054" t="inlineStr"/>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr"/>
+      <c r="F1054" t="inlineStr"/>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23433815</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>Global Geochemical and Geophysical Dataset for Cluster Analysis of Mercury's Surface</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr"/>
+      <c r="C1055" t="inlineStr"/>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr"/>
+      <c r="F1055" t="inlineStr"/>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23420970</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>Dataset of "Improving Electrolyte Sustainability for Sodium-Ion Capacitors by Combining a Bio-Based Solvent With a Low-Fluorine Salt"</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr"/>
+      <c r="C1056" t="inlineStr"/>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr"/>
+      <c r="F1056" t="inlineStr"/>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23416867</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (82-study corpus, manuscript v0.5.0)</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr"/>
+      <c r="C1057" t="inlineStr"/>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr"/>
+      <c r="F1057" t="inlineStr"/>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23428639</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1057"/>
+  <dimension ref="A1:G1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22630,6 +22630,300 @@
         </is>
       </c>
     </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>Breast cancer News Dataset 2019-2026</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr"/>
+      <c r="C1058" t="inlineStr"/>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr"/>
+      <c r="F1058" t="inlineStr"/>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/fliarbi/breast-cancer-news-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>BUSI breast ultrasound images</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr"/>
+      <c r="C1059" t="inlineStr"/>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr"/>
+      <c r="F1059" t="inlineStr"/>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/saisiddhartha23/busi-breast-ultrasound-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>Replication Package for: An Exploratory Evaluation of Targeted Label Poisoning in a Client-Local Feature Federated Ensemble for Chest X-Ray Classification</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr"/>
+      <c r="C1060" t="inlineStr"/>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr"/>
+      <c r="F1060" t="inlineStr"/>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23441636</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>A microbiome genome-wide association study of the vaginal microbiota in three Spanish sheep breeds (Dataset)</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr"/>
+      <c r="C1061" t="inlineStr"/>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr"/>
+      <c r="F1061" t="inlineStr"/>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23436276</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>Dataset related to the original article: Cleaner technologies for asphalt mixtures combining reuse of residual aggregates, waste crumb rubber and warm mix asphalt additive</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr"/>
+      <c r="C1062" t="inlineStr"/>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr"/>
+      <c r="F1062" t="inlineStr"/>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23435347</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>Non-Redundant Cryo-EM Test Dataset (2026 release targets)</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr"/>
+      <c r="C1063" t="inlineStr"/>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr"/>
+      <c r="F1063" t="inlineStr"/>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23442208</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0004 – Tribolium castaneum ATub'NLS-mB #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 2/2</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr"/>
+      <c r="C1064" t="inlineStr"/>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr"/>
+      <c r="F1064" t="inlineStr"/>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222800</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0005 – Tribolium castaneum ATub'NLS-mB #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 1/2</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr"/>
+      <c r="C1065" t="inlineStr"/>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr"/>
+      <c r="F1065" t="inlineStr"/>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222810</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0005 – Tribolium castaneum ATub'NLS-mB #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 2/2</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr"/>
+      <c r="C1066" t="inlineStr"/>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr"/>
+      <c r="F1066" t="inlineStr"/>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222829</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0006 – Tribolium castaneum ATub'NLS-mB #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 1/2</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr"/>
+      <c r="C1067" t="inlineStr"/>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr"/>
+      <c r="F1067" t="inlineStr"/>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222837</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0006 – Tribolium castaneum ATub'NLS-mB #3 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 2/2</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr"/>
+      <c r="C1068" t="inlineStr"/>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr"/>
+      <c r="F1068" t="inlineStr"/>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222853</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0007 – Tribolium castaneum 6×P3'NLS-mB #2 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 1/2</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr"/>
+      <c r="C1069" t="inlineStr"/>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr"/>
+      <c r="F1069" t="inlineStr"/>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222874</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>(16)-Ratke2026A-DS0007 – Tribolium castaneum 6×P3'NLS-mB #2 subline long-term live imaging dataset of embryonic development acquired with light sheet fluorescence microscopy – Part 2/2</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr"/>
+      <c r="C1070" t="inlineStr"/>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr"/>
+      <c r="F1070" t="inlineStr"/>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21222888</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (88-study corpus, manuscript v0.6.8)</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr"/>
+      <c r="C1071" t="inlineStr"/>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr"/>
+      <c r="F1071" t="inlineStr"/>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23450286</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1071"/>
+  <dimension ref="A1:G1076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22924,6 +22924,111 @@
         </is>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Peanut Quality Image Dataset (SNI Standard)</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr"/>
+      <c r="C1072" t="inlineStr"/>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr"/>
+      <c r="F1072" t="inlineStr"/>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/luthfimuthathohirin/kacang-tanah</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Skin Cancer Images: ISIC 2019 Preprocessed</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr"/>
+      <c r="C1073" t="inlineStr"/>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr"/>
+      <c r="F1073" t="inlineStr"/>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sudarsan007r/isic-2019-preprocessed-leakage-free-split</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Mobiusi/Microscopy-Facility-Access-And-Use-Policy-Fact-Extraction-Dataset</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr"/>
+      <c r="C1074" t="inlineStr"/>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr"/>
+      <c r="F1074" t="inlineStr"/>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/Mobiusi/Microscopy-Facility-Access-And-Use-Policy-Fact-Extraction-Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Dataset of "Fe effect in the on the OER activity of Ni based catalysts – an In-situ soft X-ray Absorption spectroscopy"</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr"/>
+      <c r="C1075" t="inlineStr"/>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr"/>
+      <c r="F1075" t="inlineStr"/>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23469502</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Example CellWorx HTD Dataset for HCS File Converter</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr"/>
+      <c r="C1076" t="inlineStr"/>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr"/>
+      <c r="F1076" t="inlineStr"/>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23468516</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1076"/>
+  <dimension ref="A1:G1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23029,6 +23029,132 @@
         </is>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Skin Lesion Segmentation Dataset</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr"/>
+      <c r="C1077" t="inlineStr"/>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr"/>
+      <c r="F1077" t="inlineStr"/>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nainhthkiu/skin-lesion-segmentation-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Coral wound-type microscopy images, 2022 and 2025</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr"/>
+      <c r="C1078" t="inlineStr"/>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr"/>
+      <c r="F1078" t="inlineStr"/>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23485154</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>CochleaNet training data for SGN segmentation, IHC segmentation and ribbon synapse detection</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr"/>
+      <c r="C1079" t="inlineStr"/>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Immunohistochemistry</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr"/>
+      <c r="F1079" t="inlineStr"/>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23478267</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>BrainSaw sst tdTomato example dataset</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr"/>
+      <c r="C1080" t="inlineStr"/>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr"/>
+      <c r="F1080" t="inlineStr"/>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23426671</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Supervised probe and diffusion reconstruction for histopathology artifact detection under magnification shift: code, adapters, probe parameters, evaluation outputs and figures</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr"/>
+      <c r="C1081" t="inlineStr"/>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr"/>
+      <c r="F1081" t="inlineStr"/>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23448122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Code, predictions and analysis for: Correction budget, not mechanism: stacking class-imbalance corrections distorts probabilities in skin lesion classification, and a one-parameter prior correction repairs it</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr"/>
+      <c r="C1082" t="inlineStr"/>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr"/>
+      <c r="F1082" t="inlineStr"/>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23477661</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1082"/>
+  <dimension ref="A1:G1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23155,6 +23155,174 @@
         </is>
       </c>
     </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>MRI-3D-Dataset</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr"/>
+      <c r="C1083" t="inlineStr"/>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr"/>
+      <c r="F1083" t="inlineStr"/>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/muhammadzahraan/mri-3d-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>NBAIR Insect Pests of India - Structured Dataset</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr"/>
+      <c r="C1084" t="inlineStr"/>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr"/>
+      <c r="F1084" t="inlineStr"/>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/souvikroybharat/nbair-insect-pests-of-india</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Dataset: Ultrasonographic time course of pyelocaliceal dilatation after laparoscopic ureteral ligation in the pig</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr"/>
+      <c r="C1085" t="inlineStr"/>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Laparoscopy</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr"/>
+      <c r="F1085" t="inlineStr"/>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23498472</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Sample Multispectral Retinal Fundus Images and Retinal Image Sequences for Ocular Disease Research</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr"/>
+      <c r="C1086" t="inlineStr"/>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr"/>
+      <c r="F1086" t="inlineStr"/>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23364391</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Dataset of the paper "Quantitative Assessment of the Hierarchical Structure of Amorphous Surfaces"</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr"/>
+      <c r="C1087" t="inlineStr"/>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr"/>
+      <c r="F1087" t="inlineStr"/>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23495781</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>CochleaNet training data for SGN segmentation, IHC segmentation and ribbon synapse detection</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr"/>
+      <c r="C1088" t="inlineStr"/>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Immunohistochemistry</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr"/>
+      <c r="F1088" t="inlineStr"/>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23500811</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Dataset for publication "Biocompatibility assessment of photocatalytic nanoparticle functionalized polyacrylonitrile nanofibers for protective textiles"</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr"/>
+      <c r="C1089" t="inlineStr"/>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr"/>
+      <c r="F1089" t="inlineStr"/>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23503650</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Supporting Raw Data Files for: Nuclear Egress Complex promotes capsid nuclear egress during Kaposi’s Sarcoma-associated herpesvirus reactivation</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr"/>
+      <c r="C1090" t="inlineStr"/>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr"/>
+      <c r="F1090" t="inlineStr"/>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/XOMAYX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1090"/>
+  <dimension ref="A1:G1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23323,6 +23323,111 @@
         </is>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>real-time-stroke-detection-in-mri-ct-pet-images</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr"/>
+      <c r="C1091" t="inlineStr"/>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr"/>
+      <c r="F1091" t="inlineStr"/>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/programmer3/real-time-stroke-detection-in-mri-ct-pet-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Mendeley Dataset for Knee Osteoporosis, Osteopenia</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr"/>
+      <c r="C1092" t="inlineStr"/>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr"/>
+      <c r="F1092" t="inlineStr"/>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/tamilin/mendekey-osteoporosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>[Dataset for] Whole-brain meso-vein imaging in living humans using fast 7-T MRI</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr"/>
+      <c r="C1093" t="inlineStr"/>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr"/>
+      <c r="F1093" t="inlineStr"/>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23316300</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>A Clinical and Ultrasound Dataset for Machine Learning-Based Pediatric Testicular Torsion Diagnosis</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr"/>
+      <c r="C1094" t="inlineStr"/>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr"/>
+      <c r="F1094" t="inlineStr"/>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23558889</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Pollen-ITA: Polygon-annotated light-microscopy images of airborne pollen and fungal spores from Italian aerobiological monitoring</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr"/>
+      <c r="C1095" t="inlineStr"/>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr"/>
+      <c r="F1095" t="inlineStr"/>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23511322</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1095"/>
+  <dimension ref="A1:G1100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23428,6 +23428,111 @@
         </is>
       </c>
     </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Alzheimer's MRI Dataset for Deep Learning</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr"/>
+      <c r="C1096" t="inlineStr"/>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr"/>
+      <c r="F1096" t="inlineStr"/>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sahilchile12/mri-images-for-federated-learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>SegWeldCT: A Dataset of High-Resolution 3D Computed Tomography Scans of Welded Joints</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr"/>
+      <c r="C1097" t="inlineStr"/>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr"/>
+      <c r="F1097" t="inlineStr"/>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23591479</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Reproduction package for Fixed-batch dynamic-range quantisation and task arithmetic for cross-dataset breast-ultrasound segmentation on single-board computers</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr"/>
+      <c r="C1098" t="inlineStr"/>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr"/>
+      <c r="F1098" t="inlineStr"/>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23577297</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Retinal OCT Classification Dataset with Grad-CAM Explainability and Controlled Intensity Perturbation</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr"/>
+      <c r="C1099" t="inlineStr"/>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr"/>
+      <c r="F1099" t="inlineStr"/>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23587962</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>QuPath pixel classifier and dataset for SARS-CoV-2 in golden Syrian hamsters</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr"/>
+      <c r="C1100" t="inlineStr"/>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr"/>
+      <c r="F1100" t="inlineStr"/>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23535439</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1100"/>
+  <dimension ref="A1:G1108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23533,6 +23533,174 @@
         </is>
       </c>
     </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>CT Scan Sarcopenia</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr"/>
+      <c r="C1101" t="inlineStr"/>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr"/>
+      <c r="F1101" t="inlineStr"/>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/leandrosaresende/ct-scan-sarcopenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>OpenSkeleton: Open, Sex-Specific Full-Body Skeletal dataset for Statistical Shape Modeling</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr"/>
+      <c r="C1102" t="inlineStr"/>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr"/>
+      <c r="F1102" t="inlineStr"/>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23592083</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>A Dataset of Reconstructed Carotid Bifurcation Lumen and Plaque Models with Centerline Tree and Simulated Hemodynamics</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr"/>
+      <c r="C1103" t="inlineStr"/>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr"/>
+      <c r="F1103" t="inlineStr"/>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23593571</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Dataset for: Innovative approach for tracking microplastics in zebrafish digestive system using micro-Computed Tomography</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr"/>
+      <c r="C1104" t="inlineStr"/>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr"/>
+      <c r="F1104" t="inlineStr"/>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/17513747</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>USCIS Changelog: USCIS Policy Manual alerts and updates (Jan 2024–Oct 2026) and core form edition dates — a Strait Research dataset</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr"/>
+      <c r="C1105" t="inlineStr"/>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr"/>
+      <c r="F1105" t="inlineStr"/>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23608230</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Rule Watch: U.S. immigration rulemaking in the Federal Register, 24 Oct 2025 – 23 Oct 2026 — a Strait Research dataset</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr"/>
+      <c r="C1106" t="inlineStr"/>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr"/>
+      <c r="F1106" t="inlineStr"/>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23607763</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Dataset for publication Advanced Flexible Bioelectrodes for Next-Generation Implantable Triboelectric Nanogenerators</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr"/>
+      <c r="C1107" t="inlineStr"/>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr"/>
+      <c r="F1107" t="inlineStr"/>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23206546</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Imaging Biomarkers of Neurofibromatosis Type 1-Associated Optic Pathway Glioma</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr"/>
+      <c r="C1108" t="inlineStr"/>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr"/>
+      <c r="F1108" t="inlineStr"/>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn4939894</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1108"/>
+  <dimension ref="A1:G1119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23701,6 +23701,237 @@
         </is>
       </c>
     </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Heaton &amp; Associates, PLLC AI Knowledge Dataset</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr"/>
+      <c r="C1109" t="inlineStr"/>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr"/>
+      <c r="F1109" t="inlineStr"/>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/aiovisibilityhub/heaton-associates-pllc-ai-schemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>MCND dataset - Multi-Class Brain MRI Scans</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr"/>
+      <c r="C1110" t="inlineStr"/>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr"/>
+      <c r="F1110" t="inlineStr"/>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/alifatahi/mcnd-dataset-multi-class-brain-mri-scans</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>GAMMA Challenge Dataset</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr"/>
+      <c r="C1111" t="inlineStr"/>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr"/>
+      <c r="F1111" t="inlineStr"/>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nebuplacid/gamma-challenge-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>67ll/NAGNet-MRI-Dataset</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr"/>
+      <c r="C1112" t="inlineStr"/>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr"/>
+      <c r="F1112" t="inlineStr"/>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/67ll/NAGNet-MRI-Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>rijal028/ultrasound-skala-dataset</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr"/>
+      <c r="C1113" t="inlineStr"/>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr"/>
+      <c r="F1113" t="inlineStr"/>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/rijal028/ultrasound-skala-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>X-ray CT projection dataset of a metallic foam, metal pin and layered marker test object (Diamond Light Source I12, 2009)</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr"/>
+      <c r="C1114" t="inlineStr"/>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr"/>
+      <c r="F1114" t="inlineStr"/>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23623238</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Dataset for geochemical and spectroscopic hyperspectral point data analysis on metavolcanic soils and sulfide-derived mine waste piles in the Trimpancho Mining Site (Iberian Pyrite Belt, Spain)</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr"/>
+      <c r="C1115" t="inlineStr"/>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr"/>
+      <c r="F1115" t="inlineStr"/>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23120884</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Rule Watch: U.S. immigration rulemaking in the Federal Register, 24 Oct 2025 – 23 Oct 2026 — a Strait Research dataset</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr"/>
+      <c r="C1116" t="inlineStr"/>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr"/>
+      <c r="F1116" t="inlineStr"/>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23624687</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Policy Attention Index: daily DAP visits to USCIS, ICE, CBP and Department of Justice web domains, Jan 2025 - Oct 2026 - a Strait Research dataset</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr"/>
+      <c r="C1117" t="inlineStr"/>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr"/>
+      <c r="F1117" t="inlineStr"/>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23624440</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Hidden-Curriculum Atlas: College Scorecard outcomes, completion, debt, earnings, Pell, first-generation and low-income shares for 5,828 U.S. institutions (latest release, retrieved 24 Oct 2026) — a Strait Research dataset</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr"/>
+      <c r="C1118" t="inlineStr"/>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr"/>
+      <c r="F1118" t="inlineStr"/>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23624393</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>USCIS Changelog: USCIS Policy Manual alerts and updates (Jan 2024–Oct 2026) and core form edition dates — a Strait Research dataset</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr"/>
+      <c r="C1119" t="inlineStr"/>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr"/>
+      <c r="F1119" t="inlineStr"/>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23622524</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1119"/>
+  <dimension ref="A1:G1129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23932,6 +23932,216 @@
         </is>
       </c>
     </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Lahore Board Intermediate Dataset Challange</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr"/>
+      <c r="C1120" t="inlineStr"/>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr"/>
+      <c r="F1120" t="inlineStr"/>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/arslanabdulshakoor/bise-lahore-inter-dataset-challange</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Unified Crop Pathology Dataset 194 Classes</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr"/>
+      <c r="C1121" t="inlineStr"/>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr"/>
+      <c r="F1121" t="inlineStr"/>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dhanushnagisetti/unified-crop-pathology-dataset-194-classes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>ISIC 2019 External Skin Lesion Dataset - 7 Classes</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr"/>
+      <c r="C1122" t="inlineStr"/>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr"/>
+      <c r="F1122" t="inlineStr"/>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dhruvone8/isic-2019-external-skin-lesion-dataset-7-classes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>X-ray CT projection and reconstruction dataset of a titanium bar with ring artefacts (Diamond Light Source I12, 2009)</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr"/>
+      <c r="C1123" t="inlineStr"/>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr"/>
+      <c r="F1123" t="inlineStr"/>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23642139</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>PAXRay++ (PAXRayPP): A dataset for Fine-Grained Segmentation of Thoracic Anatomy in Chest Radiographs via Volumetric Pseudo-Labeling</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr"/>
+      <c r="C1124" t="inlineStr"/>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr"/>
+      <c r="F1124" t="inlineStr"/>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23627483</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>X-ray CT projection dataset of a coral specimen with strong ring artefacts (Diamond Light Source I12, 2009)</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr"/>
+      <c r="C1125" t="inlineStr"/>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr"/>
+      <c r="F1125" t="inlineStr"/>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23652680</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Parallel-beam X-ray CT projection and reconstruction dataset of a cylindrical composite-material bar with ring artefacts and scattered bright pixels (Diamond Light Source I12, 2008)</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr"/>
+      <c r="C1126" t="inlineStr"/>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr"/>
+      <c r="F1126" t="inlineStr"/>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23652033</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>X-ray CT projection dataset of a composite plate with scintillator and distortion artefacts (Diamond Light Source I12, 2009)</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr"/>
+      <c r="C1127" t="inlineStr"/>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr"/>
+      <c r="F1127" t="inlineStr"/>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23645730</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Bayesian Sequential Interpretation of Two Separately Developed AI Systems for Glaucoma Classification from the Same Fundus Photographs</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr"/>
+      <c r="C1128" t="inlineStr"/>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr"/>
+      <c r="F1128" t="inlineStr"/>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23644833</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Deep-UV lensless holographic microscopy on visible CMOS sensors for low-dose centimeter-scale biochemical imaging - Dataset</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr"/>
+      <c r="C1129" t="inlineStr"/>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr"/>
+      <c r="F1129" t="inlineStr"/>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23598529</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1129"/>
+  <dimension ref="A1:G1137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24142,6 +24142,174 @@
         </is>
       </c>
     </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sri Lanka Job Postings &amp; Salaries Dataset </t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr"/>
+      <c r="C1130" t="inlineStr"/>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr"/>
+      <c r="F1130" t="inlineStr"/>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sahilkavishkakumara/sri-lanka-job-postings-and-vacancies-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Spectron Electron Microscope Images</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr"/>
+      <c r="C1131" t="inlineStr"/>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr"/>
+      <c r="F1131" t="inlineStr"/>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/researcharchivee/spectron-electron-microscope-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>BUS-BRA dataset</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr"/>
+      <c r="C1132" t="inlineStr"/>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr"/>
+      <c r="F1132" t="inlineStr"/>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sadianazninananna/bus-bra-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Supporting analytical dataset for "Multi-method characterization of rock crystal quartz from the Yüksekova ophiolitic mélange (Yeşiltaş, Hakkari, SE Türkiye)": XRD, Raman, FTIR, UV-Vis-NIR, SEM-EDS and whole-rock geochemical data</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr"/>
+      <c r="C1133" t="inlineStr"/>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr"/>
+      <c r="F1133" t="inlineStr"/>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21994213</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Reproduction package: Evaluation of machine learning representations for trace asbestos detection in recycled gypsum using wide-angle X-ray scattering</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr"/>
+      <c r="C1134" t="inlineStr"/>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr"/>
+      <c r="F1134" t="inlineStr"/>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23667894</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Dataset for the "Mapping the parameter space of double microwave shielding" paper</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr"/>
+      <c r="C1135" t="inlineStr"/>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr"/>
+      <c r="F1135" t="inlineStr"/>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23667930</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Experimental dataset for porosity as a function of processing parameters in PBF-LB AM of AlNiCo 8 alloy</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr"/>
+      <c r="C1136" t="inlineStr"/>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr"/>
+      <c r="F1136" t="inlineStr"/>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23390302</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Microscopy and SEM Images of Residues from the RR2010 Grinding Stone, Lucone D</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr"/>
+      <c r="C1137" t="inlineStr"/>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr"/>
+      <c r="F1137" t="inlineStr"/>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23235496</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1137"/>
+  <dimension ref="A1:G1144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24310,6 +24310,153 @@
         </is>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>BraTS 2020 Brain Tumor Segmentation U-Net Weights</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr"/>
+      <c r="C1138" t="inlineStr"/>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr"/>
+      <c r="F1138" t="inlineStr"/>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/akhilnathreddy/brats2020-unet-segmentation-weights</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>DATASET OF TRAIN(CSV)-DVT_ULTRASOUND IMAGES FRAMES</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr"/>
+      <c r="C1139" t="inlineStr"/>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr"/>
+      <c r="F1139" t="inlineStr"/>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/abdullahmohsinune/dataset-of-traincsv-dvt-ultrasound-images-frames</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>DELTA-SVD longitudinal release regression dataset</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr"/>
+      <c r="C1140" t="inlineStr"/>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr"/>
+      <c r="F1140" t="inlineStr"/>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23723917</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Micro CBCT half-scan of a 10 week old male mouse using the GE eXplore CT 120 scanner and a lung-gated step-and-shoot protocol</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr"/>
+      <c r="C1141" t="inlineStr"/>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>CBCT</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr"/>
+      <c r="F1141" t="inlineStr"/>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23709630</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Rule Watch: U.S. immigration rulemaking in the Federal Register, 28 Oct 2025 – 27 Oct 2026 — a Strait Research dataset</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr"/>
+      <c r="C1142" t="inlineStr"/>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr"/>
+      <c r="F1142" t="inlineStr"/>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23692597</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Provenance audit of the CTCB benchmark: evidence graph, grouped split, preregistration documents, notebooks and per-image predictions</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr"/>
+      <c r="C1143" t="inlineStr"/>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr"/>
+      <c r="F1143" t="inlineStr"/>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23672475</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Run records for a knowledge-distillation benchmark of pathology foundation models</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr"/>
+      <c r="C1144" t="inlineStr"/>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr"/>
+      <c r="F1144" t="inlineStr"/>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23718451</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1144"/>
+  <dimension ref="A1:G1155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24457,6 +24457,237 @@
         </is>
       </c>
     </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Multi-sequence brain MRI MS  Dataset</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr"/>
+      <c r="C1145" t="inlineStr"/>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr"/>
+      <c r="F1145" t="inlineStr"/>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/suleyman32/multi-sequence-brain-mri-ms-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Rainy-fog/Cervical-Histopathology-Tile-Classification</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr"/>
+      <c r="C1146" t="inlineStr"/>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr"/>
+      <c r="F1146" t="inlineStr"/>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/Rainy-fog/Cervical-Histopathology-Tile-Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>ISLES (Ischemic Stroke Lesion Segmentation/Prediction) Challenge Datasets 2017 Testing with Labels</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr"/>
+      <c r="C1147" t="inlineStr"/>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr"/>
+      <c r="F1147" t="inlineStr"/>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23760681</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Curated Dataset of 430 Studies on fMRI-to-Image Reconstruction A PRISMA 2020-Guided Systematic Review and Bibliometric Analysis</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr"/>
+      <c r="C1148" t="inlineStr"/>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr"/>
+      <c r="F1148" t="inlineStr"/>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23740578</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>CT scan of a fossilized bryozoan with bioerosional trace fossils, specimen GIT 537-4714</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr"/>
+      <c r="C1149" t="inlineStr"/>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr"/>
+      <c r="F1149" t="inlineStr"/>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23593551</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>CT scan of a fossilized bryozoan with bioerosional trace fossils, specimen GIT 537-4715</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr"/>
+      <c r="C1150" t="inlineStr"/>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr"/>
+      <c r="F1150" t="inlineStr"/>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22871632</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>HexaMagDB: a dataset of magnetic properties, structure and synthesis of doped barium and strontium M-type hexaferrites</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr"/>
+      <c r="C1151" t="inlineStr"/>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr"/>
+      <c r="F1151" t="inlineStr"/>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23759532</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>SEPFLOW: A High-Resolution Multivariate Time-Series Dataset for Solar Energetic Particle Forecasting</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr"/>
+      <c r="C1152" t="inlineStr"/>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr"/>
+      <c r="F1152" t="inlineStr"/>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23747778</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Synthetic and Real Image Dataset for Metrological Validation of AI-Based Circle Detection</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr"/>
+      <c r="C1153" t="inlineStr"/>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr"/>
+      <c r="F1153" t="inlineStr"/>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23757601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>CrossWave Raw Dataset: Multi-Wavelength iSCAT Imaging of Lipid Nanoparticles for Size-Proxy Prediction</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr"/>
+      <c r="C1154" t="inlineStr"/>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr"/>
+      <c r="F1154" t="inlineStr"/>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23547747</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Run records for a knowledge-distillation benchmark of pathology foundation models</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr"/>
+      <c r="C1155" t="inlineStr"/>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr"/>
+      <c r="F1155" t="inlineStr"/>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23718759</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1155"/>
+  <dimension ref="A1:G1169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24688,6 +24688,300 @@
         </is>
       </c>
     </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Dataset: Three-Dimensional Mineral–Fracture Relationships in Martian Chassignite NWA 2737: Constraints on Crystallization Sequence and Impact–Thermal Evolution</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr"/>
+      <c r="C1156" t="inlineStr"/>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr"/>
+      <c r="F1156" t="inlineStr"/>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23779572</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Ocular Proton Therapy (AAPM Task Group 418) Planning dataset 8 (superior location)</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr"/>
+      <c r="C1157" t="inlineStr"/>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr"/>
+      <c r="F1157" t="inlineStr"/>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23768923</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Ocular Proton Therapy (AAPM Task Group 418) Planning dataset 6 (polar tumor location)</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr"/>
+      <c r="C1158" t="inlineStr"/>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr"/>
+      <c r="F1158" t="inlineStr"/>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23768594</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Ocular Proton Therapy (AAPM Task Group 418) Planning dataset 4 (temporal tumor location)</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr"/>
+      <c r="C1159" t="inlineStr"/>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr"/>
+      <c r="F1159" t="inlineStr"/>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23768273</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Three-dimensional X-ray microtomography dataset of Laacher See and Vesuvius pumice before and after experimental tumbling</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr"/>
+      <c r="C1160" t="inlineStr"/>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr"/>
+      <c r="F1160" t="inlineStr"/>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23804010</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>pXRF screening dataset for non-ferrous artefacts from Unguja Ukuu, Zanzibar</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr"/>
+      <c r="C1161" t="inlineStr"/>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr"/>
+      <c r="F1161" t="inlineStr"/>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23440327</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Dataset for "Contrasting fate of holes introduced by Fe or In in kagome metal CoSn"</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr"/>
+      <c r="C1162" t="inlineStr"/>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr"/>
+      <c r="F1162" t="inlineStr"/>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23539503</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>VetXRay -  A Dataset of 9,882 Manually Annotated Canine and Feline Thoracic Radiographs with Lesion and Image Quality Annotations</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr"/>
+      <c r="C1163" t="inlineStr"/>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr"/>
+      <c r="F1163" t="inlineStr"/>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23762009</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Private Medical Image Segmentation on a Single Untrusted Server: A Homomorphic Encryption-Compatible Architecture and Its Measured Cost — code and data</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr"/>
+      <c r="C1164" t="inlineStr"/>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr"/>
+      <c r="F1164" t="inlineStr"/>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23771403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>GenMC: In Vivo Photoacoustic and Ultrasound Dataset for Blood Oxygen Saturation Estimation</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr"/>
+      <c r="C1165" t="inlineStr"/>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr"/>
+      <c r="F1165" t="inlineStr"/>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23768761</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Linked collectors and determiners for: Records of the DAFWA Plant Pathology Collection.</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr"/>
+      <c r="C1166" t="inlineStr"/>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr"/>
+      <c r="F1166" t="inlineStr"/>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23785452</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Superscan caused by renal osteodystrophy: Observed on 18F FDG PET/CT scan</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr"/>
+      <c r="C1167" t="inlineStr"/>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr"/>
+      <c r="F1167" t="inlineStr"/>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/235/3866677/PMC3866677_IJNM-28-251-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Therapeutic effect of curcumin nanoemulsion on cystic echinococcosis in BALB/c mice: a computerized tomography (CT) scan and histopathologic study evaluation</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr"/>
+      <c r="C1168" t="inlineStr"/>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr"/>
+      <c r="F1168" t="inlineStr"/>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/121/10993536/PMC10993536_12906_2024_4451_Fig4_HTML.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Correlations of CT scan with high-sensitivity C-reactive protein and D-dimer in patients with coronavirus disease 2019</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr"/>
+      <c r="C1169" t="inlineStr"/>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr"/>
+      <c r="F1169" t="inlineStr"/>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://openi.nlm.nih.gov/detailedresult?img=/imgs/512/297/7501002/PMC7501002_PJMS-36-1397-g002.png&amp;req=4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1169"/>
+  <dimension ref="A1:G1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24982,6 +24982,216 @@
         </is>
       </c>
     </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>A 10-μm isotropic whole-brain PS-OCT dataset with a paired 9.4-T MRI subset in mice</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr"/>
+      <c r="C1170" t="inlineStr"/>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr"/>
+      <c r="F1170" t="inlineStr"/>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23530831</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>Derived data and analysed micro-CT stacks for "Support, Resolution and Segmentation Effects on Micro-CT Estimates of Porosity, Specific Surface and Box-Counting Dimension in Carbonate Rocks"</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr"/>
+      <c r="C1171" t="inlineStr"/>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr"/>
+      <c r="F1171" t="inlineStr"/>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23818173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>3D hyperspectral dataset of NMC grains for broadband ptychographic tomography</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr"/>
+      <c r="C1172" t="inlineStr"/>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr"/>
+      <c r="F1172" t="inlineStr"/>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23189401</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>Dataset: Research Data for Publication "Microstructure development in LiBH4-MgH2 RHC upon temperature change and repeated cycling"</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr"/>
+      <c r="C1173" t="inlineStr"/>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr"/>
+      <c r="F1173" t="inlineStr"/>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23799593</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>HexaMagDB: a dataset of magnetic properties, structure and synthesis of doped barium and strontium M-type hexaferrites</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr"/>
+      <c r="C1174" t="inlineStr"/>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr"/>
+      <c r="F1174" t="inlineStr"/>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23807417</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>LT-STM dataset, Schofield group, UCL</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr"/>
+      <c r="C1175" t="inlineStr"/>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr"/>
+      <c r="F1175" t="inlineStr"/>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23808255</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>Supporting dataset (Supplementary Tables S1-S8) for High-resolution spatial transcriptome of the human female gonad</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr"/>
+      <c r="C1176" t="inlineStr"/>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr"/>
+      <c r="F1176" t="inlineStr"/>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23825446</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>Fairness in histopathology AI — systematic review: extraction, audit, and verification artifacts (88-study corpus, manuscript v0.6.10)</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr"/>
+      <c r="C1177" t="inlineStr"/>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr"/>
+      <c r="F1177" t="inlineStr"/>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/23825249</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>Pomelo CT Scans</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr"/>
+      <c r="C1178" t="inlineStr"/>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr"/>
+      <c r="F1178" t="inlineStr"/>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/PP9DHU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>OMEGA-FIELD: A Prospective Field Validation Study of Tourniquet Performance and Human Factors</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr"/>
+      <c r="C1179" t="inlineStr"/>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Doppler Ultrasound</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr"/>
+      <c r="F1179" t="inlineStr"/>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/FLT4V1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
